--- a/public/data/veritrace-dataset.xlsx
+++ b/public/data/veritrace-dataset.xlsx
@@ -17,7 +17,8 @@
     <sheet name="Trading Partners" sheetId="12" r:id="rId12"/>
     <sheet name="Risk Events" sheetId="13" r:id="rId13"/>
     <sheet name="Recalls" sheetId="14" r:id="rId14"/>
-    <sheet name="Ask Me" sheetId="15" r:id="rId15"/>
+    <sheet name="Shipments Denormalized" sheetId="15" r:id="rId15"/>
+    <sheet name="Ask Me" sheetId="16" r:id="rId16"/>
   </sheets>
 </workbook>
 </file>
@@ -39812,6 +39813,9911 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:BL51"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>shipment_id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>status</v>
+      </c>
+      <c r="C1" t="str">
+        <v>primary_mode</v>
+      </c>
+      <c r="D1" t="str">
+        <v>delay_hours</v>
+      </c>
+      <c r="E1" t="str">
+        <v>package_count</v>
+      </c>
+      <c r="F1" t="str">
+        <v>departed_at</v>
+      </c>
+      <c r="G1" t="str">
+        <v>eta_at</v>
+      </c>
+      <c r="H1" t="str">
+        <v>delivered_at</v>
+      </c>
+      <c r="I1" t="str">
+        <v>has_excursion</v>
+      </c>
+      <c r="J1" t="str">
+        <v>traceability_complete</v>
+      </c>
+      <c r="K1" t="str">
+        <v>current_location</v>
+      </c>
+      <c r="L1" t="str">
+        <v>product_id</v>
+      </c>
+      <c r="M1" t="str">
+        <v>product_name</v>
+      </c>
+      <c r="N1" t="str">
+        <v>drug_category</v>
+      </c>
+      <c r="O1" t="str">
+        <v>storage_requirement</v>
+      </c>
+      <c r="P1" t="str">
+        <v>temp_min_c</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>temp_max_c</v>
+      </c>
+      <c r="R1" t="str">
+        <v>gtin</v>
+      </c>
+      <c r="S1" t="str">
+        <v>batch_number</v>
+      </c>
+      <c r="T1" t="str">
+        <v>manufacturing_date</v>
+      </c>
+      <c r="U1" t="str">
+        <v>expiration_date</v>
+      </c>
+      <c r="V1" t="str">
+        <v>manufacturer_name</v>
+      </c>
+      <c r="W1" t="str">
+        <v>manufacturer_country</v>
+      </c>
+      <c r="X1" t="str">
+        <v>batch_unit_count</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>carrier_id</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>carrier_name</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>carrier_modes</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>carrier_on_time_pct</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>carrier_performance_score</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>origin_id</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>origin_name</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>origin_type</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>origin_country</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>origin_lat</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>origin_lng</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>destination_id</v>
+      </c>
+      <c r="AK1" t="str">
+        <v>destination_name</v>
+      </c>
+      <c r="AL1" t="str">
+        <v>destination_type</v>
+      </c>
+      <c r="AM1" t="str">
+        <v>destination_country</v>
+      </c>
+      <c r="AN1" t="str">
+        <v>destination_lat</v>
+      </c>
+      <c r="AO1" t="str">
+        <v>destination_lng</v>
+      </c>
+      <c r="AP1" t="str">
+        <v>event_count</v>
+      </c>
+      <c r="AQ1" t="str">
+        <v>custody_event_count</v>
+      </c>
+      <c r="AR1" t="str">
+        <v>custody_gap_count</v>
+      </c>
+      <c r="AS1" t="str">
+        <v>ownership_transfer_count</v>
+      </c>
+      <c r="AT1" t="str">
+        <v>ownership_chain</v>
+      </c>
+      <c r="AU1" t="str">
+        <v>temp_reading_count</v>
+      </c>
+      <c r="AV1" t="str">
+        <v>temp_min_observed</v>
+      </c>
+      <c r="AW1" t="str">
+        <v>temp_max_observed</v>
+      </c>
+      <c r="AX1" t="str">
+        <v>temp_avg_observed</v>
+      </c>
+      <c r="AY1" t="str">
+        <v>excursion_reading_count</v>
+      </c>
+      <c r="AZ1" t="str">
+        <v>risk_event_count</v>
+      </c>
+      <c r="BA1" t="str">
+        <v>open_risk_count</v>
+      </c>
+      <c r="BB1" t="str">
+        <v>risk_delay</v>
+      </c>
+      <c r="BC1" t="str">
+        <v>risk_temperature_excursion</v>
+      </c>
+      <c r="BD1" t="str">
+        <v>risk_route_deviation</v>
+      </c>
+      <c r="BE1" t="str">
+        <v>risk_missing_scan</v>
+      </c>
+      <c r="BF1" t="str">
+        <v>risk_unauthorized_transfer</v>
+      </c>
+      <c r="BG1" t="str">
+        <v>environmental_conditions</v>
+      </c>
+      <c r="BH1" t="str">
+        <v>recall_id</v>
+      </c>
+      <c r="BI1" t="str">
+        <v>recall_status</v>
+      </c>
+      <c r="BJ1" t="str">
+        <v>recall_impacted_packages</v>
+      </c>
+      <c r="BK1" t="str">
+        <v>recall_located_packages</v>
+      </c>
+      <c r="BL1" t="str">
+        <v>recall_outstanding_packages</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SHP-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>IN_TRANSIT</v>
+      </c>
+      <c r="C2" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="D2">
+        <v>18</v>
+      </c>
+      <c r="E2">
+        <v>1960</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2026-06-13T12:00:00.000Z</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2026-06-26T12:00:00.000Z</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L2" t="str">
+        <v>prod-covid</v>
+      </c>
+      <c r="M2" t="str">
+        <v>COVID-19 mRNA Vaccine</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Vaccine (Biologic)</v>
+      </c>
+      <c r="O2" t="str">
+        <v>Cold chain 2–8°C</v>
+      </c>
+      <c r="P2">
+        <v>2</v>
+      </c>
+      <c r="Q2">
+        <v>8</v>
+      </c>
+      <c r="R2" t="str">
+        <v>03000000000017</v>
+      </c>
+      <c r="S2" t="str">
+        <v>VX-2026-001</v>
+      </c>
+      <c r="T2" t="str">
+        <v>2026-04-26T12:00:00.000Z</v>
+      </c>
+      <c r="U2" t="str">
+        <v>2027-04-26T12:00:00.000Z</v>
+      </c>
+      <c r="V2" t="str">
+        <v>BioNTech Marburg GmbH</v>
+      </c>
+      <c r="W2" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="X2">
+        <v>24500</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>car-a</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>Atlantic Ocean Lines</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="AB2">
+        <v>100</v>
+      </c>
+      <c r="AC2">
+        <v>66</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>loc-mfg-de</v>
+      </c>
+      <c r="AE2" t="str">
+        <v>BioNTech Manufacturing — Marburg</v>
+      </c>
+      <c r="AF2" t="str">
+        <v>MANUFACTURER</v>
+      </c>
+      <c r="AG2" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH2">
+        <v>50.8093</v>
+      </c>
+      <c r="AI2">
+        <v>8.7708</v>
+      </c>
+      <c r="AJ2" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK2" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL2" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM2" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN2">
+        <v>40.7903</v>
+      </c>
+      <c r="AO2">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP2">
+        <v>8</v>
+      </c>
+      <c r="AQ2">
+        <v>6</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>2</v>
+      </c>
+      <c r="AT2" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU2">
+        <v>97</v>
+      </c>
+      <c r="AV2">
+        <v>2.8</v>
+      </c>
+      <c r="AW2">
+        <v>10</v>
+      </c>
+      <c r="AX2">
+        <v>5.2</v>
+      </c>
+      <c r="AY2">
+        <v>7</v>
+      </c>
+      <c r="AZ2">
+        <v>2</v>
+      </c>
+      <c r="BA2">
+        <v>2</v>
+      </c>
+      <c r="BB2">
+        <v>1</v>
+      </c>
+      <c r="BC2">
+        <v>1</v>
+      </c>
+      <c r="BD2">
+        <v>0</v>
+      </c>
+      <c r="BE2">
+        <v>0</v>
+      </c>
+      <c r="BF2">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="str">
+        <v>North Atlantic Storm System | Customs Congestion — Newark | Heatwave — US Northeast | Fog — Port of Hamburg</v>
+      </c>
+      <c r="BH2" t="str">
+        <v>RCL-2026-001</v>
+      </c>
+      <c r="BI2" t="str">
+        <v>OPEN</v>
+      </c>
+      <c r="BJ2">
+        <v>24500</v>
+      </c>
+      <c r="BK2">
+        <v>24120</v>
+      </c>
+      <c r="BL2">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SHP-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>DELAYED</v>
+      </c>
+      <c r="C3" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="D3">
+        <v>23</v>
+      </c>
+      <c r="E3">
+        <v>827</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2026-05-23T12:00:00.000Z</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2026-06-30T12:00:00.000Z</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L3" t="str">
+        <v>prod-mab</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Monoclonal Antibody Infusion</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Biologic (Oncology)</v>
+      </c>
+      <c r="O3" t="str">
+        <v>Cold chain 2–8°C</v>
+      </c>
+      <c r="P3">
+        <v>2</v>
+      </c>
+      <c r="Q3">
+        <v>8</v>
+      </c>
+      <c r="R3" t="str">
+        <v>03000000000031</v>
+      </c>
+      <c r="S3" t="str">
+        <v>BN-2026-006</v>
+      </c>
+      <c r="T3" t="str">
+        <v>2026-01-17T12:00:00.000Z</v>
+      </c>
+      <c r="U3" t="str">
+        <v>2027-01-21T12:00:00.000Z</v>
+      </c>
+      <c r="V3" t="str">
+        <v>Generic Pharma Mumbai Ltd</v>
+      </c>
+      <c r="W3" t="str">
+        <v>India</v>
+      </c>
+      <c r="X3">
+        <v>14000</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>car-a</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>Atlantic Ocean Lines</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="AB3">
+        <v>100</v>
+      </c>
+      <c r="AC3">
+        <v>66</v>
+      </c>
+      <c r="AD3" t="str">
+        <v>loc-port-hamburg</v>
+      </c>
+      <c r="AE3" t="str">
+        <v>Port of Hamburg</v>
+      </c>
+      <c r="AF3" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG3" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH3">
+        <v>53.5413</v>
+      </c>
+      <c r="AI3">
+        <v>9.9326</v>
+      </c>
+      <c r="AJ3" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK3" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL3" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM3" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN3">
+        <v>33.749</v>
+      </c>
+      <c r="AO3">
+        <v>-84.388</v>
+      </c>
+      <c r="AP3">
+        <v>6</v>
+      </c>
+      <c r="AQ3">
+        <v>6</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>2</v>
+      </c>
+      <c r="AT3" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU3">
+        <v>265</v>
+      </c>
+      <c r="AV3">
+        <v>2.9</v>
+      </c>
+      <c r="AW3">
+        <v>7.4</v>
+      </c>
+      <c r="AX3">
+        <v>5.1</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>2</v>
+      </c>
+      <c r="BA3">
+        <v>1</v>
+      </c>
+      <c r="BB3">
+        <v>1</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>1</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="str">
+        <v>North Atlantic Storm System | Customs Congestion — Newark | Heatwave — US Northeast | Fog — Port of Hamburg</v>
+      </c>
+      <c r="BH3" t="str">
+        <v/>
+      </c>
+      <c r="BI3" t="str">
+        <v/>
+      </c>
+      <c r="BJ3" t="str">
+        <v/>
+      </c>
+      <c r="BK3" t="str">
+        <v/>
+      </c>
+      <c r="BL3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SHP-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C4" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>866</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2026-06-18T12:00:00.000Z</v>
+      </c>
+      <c r="G4" t="str">
+        <v>2026-06-22T12:00:00.000Z</v>
+      </c>
+      <c r="H4" t="str">
+        <v>2026-06-22T12:00:00.000Z</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L4" t="str">
+        <v>prod-salbutamol</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Salbutamol Inhaler</v>
+      </c>
+      <c r="N4" t="str">
+        <v>Respiratory</v>
+      </c>
+      <c r="O4" t="str">
+        <v>Controlled room 15–25°C</v>
+      </c>
+      <c r="P4">
+        <v>15</v>
+      </c>
+      <c r="Q4">
+        <v>25</v>
+      </c>
+      <c r="R4" t="str">
+        <v>03000000000109</v>
+      </c>
+      <c r="S4" t="str">
+        <v>BN-2026-005</v>
+      </c>
+      <c r="T4" t="str">
+        <v>2026-02-01T12:00:00.000Z</v>
+      </c>
+      <c r="U4" t="str">
+        <v>2027-03-21T12:00:00.000Z</v>
+      </c>
+      <c r="V4" t="str">
+        <v>BioNTech Marburg GmbH</v>
+      </c>
+      <c r="W4" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="X4">
+        <v>5000</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>car-h</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>Global Air Freight</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="AB4">
+        <v>75</v>
+      </c>
+      <c r="AC4">
+        <v>63</v>
+      </c>
+      <c r="AD4" t="str">
+        <v>loc-air-fra</v>
+      </c>
+      <c r="AE4" t="str">
+        <v>Frankfurt Air Cargo Hub</v>
+      </c>
+      <c r="AF4" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG4" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH4">
+        <v>50.0379</v>
+      </c>
+      <c r="AI4">
+        <v>8.5622</v>
+      </c>
+      <c r="AJ4" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK4" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL4" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM4" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN4">
+        <v>40.7903</v>
+      </c>
+      <c r="AO4">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP4">
+        <v>5</v>
+      </c>
+      <c r="AQ4">
+        <v>6</v>
+      </c>
+      <c r="AR4">
+        <v>1</v>
+      </c>
+      <c r="AS4">
+        <v>2</v>
+      </c>
+      <c r="AT4" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="str">
+        <v/>
+      </c>
+      <c r="AW4" t="str">
+        <v/>
+      </c>
+      <c r="AX4" t="str">
+        <v/>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH4" t="str">
+        <v>RCL-2025-014</v>
+      </c>
+      <c r="BI4" t="str">
+        <v>CLOSED</v>
+      </c>
+      <c r="BJ4">
+        <v>5200</v>
+      </c>
+      <c r="BK4">
+        <v>5200</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>SHP-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>IN_TRANSIT</v>
+      </c>
+      <c r="C5" t="str">
+        <v>RAIL</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>479</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2026-06-23T12:00:00.000Z</v>
+      </c>
+      <c r="G5" t="str">
+        <v>2026-07-05T12:00:00.000Z</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L5" t="str">
+        <v>prod-flu</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Influenza Vaccine</v>
+      </c>
+      <c r="N5" t="str">
+        <v>Vaccine</v>
+      </c>
+      <c r="O5" t="str">
+        <v>Cold chain 2–8°C</v>
+      </c>
+      <c r="P5">
+        <v>2</v>
+      </c>
+      <c r="Q5">
+        <v>8</v>
+      </c>
+      <c r="R5" t="str">
+        <v>03000000000048</v>
+      </c>
+      <c r="S5" t="str">
+        <v>BN-2026-003</v>
+      </c>
+      <c r="T5" t="str">
+        <v>2026-05-03T12:00:00.000Z</v>
+      </c>
+      <c r="U5" t="str">
+        <v>2027-06-08T12:00:00.000Z</v>
+      </c>
+      <c r="V5" t="str">
+        <v>BioNTech Marburg GmbH</v>
+      </c>
+      <c r="W5" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="X5">
+        <v>36000</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>car-f</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>EuroRail Logistics</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>RAIL | TRUCK</v>
+      </c>
+      <c r="AB5">
+        <v>100</v>
+      </c>
+      <c r="AC5">
+        <v>62</v>
+      </c>
+      <c r="AD5" t="str">
+        <v>loc-port-la</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>Port of Los Angeles</v>
+      </c>
+      <c r="AF5" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG5" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AH5">
+        <v>33.7395</v>
+      </c>
+      <c r="AI5">
+        <v>-118.2597</v>
+      </c>
+      <c r="AJ5" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK5" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL5" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM5" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN5">
+        <v>40.7903</v>
+      </c>
+      <c r="AO5">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP5">
+        <v>3</v>
+      </c>
+      <c r="AQ5">
+        <v>6</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>2</v>
+      </c>
+      <c r="AT5" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU5">
+        <v>17</v>
+      </c>
+      <c r="AV5">
+        <v>3.7</v>
+      </c>
+      <c r="AW5">
+        <v>6.1</v>
+      </c>
+      <c r="AX5">
+        <v>4.9</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast | Port Congestion — Los Angeles</v>
+      </c>
+      <c r="BH5" t="str">
+        <v/>
+      </c>
+      <c r="BI5" t="str">
+        <v/>
+      </c>
+      <c r="BJ5" t="str">
+        <v/>
+      </c>
+      <c r="BK5" t="str">
+        <v/>
+      </c>
+      <c r="BL5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>SHP-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CUSTOMS_HOLD</v>
+      </c>
+      <c r="C6" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>1483</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2026-06-16T12:00:00.000Z</v>
+      </c>
+      <c r="G6" t="str">
+        <v>2026-07-03T12:00:00.000Z</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L6" t="str">
+        <v>prod-salbutamol</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Salbutamol Inhaler</v>
+      </c>
+      <c r="N6" t="str">
+        <v>Respiratory</v>
+      </c>
+      <c r="O6" t="str">
+        <v>Controlled room 15–25°C</v>
+      </c>
+      <c r="P6">
+        <v>15</v>
+      </c>
+      <c r="Q6">
+        <v>25</v>
+      </c>
+      <c r="R6" t="str">
+        <v>03000000000109</v>
+      </c>
+      <c r="S6" t="str">
+        <v>BN-2026-019</v>
+      </c>
+      <c r="T6" t="str">
+        <v>2026-04-27T12:00:00.000Z</v>
+      </c>
+      <c r="U6" t="str">
+        <v>2027-12-08T12:00:00.000Z</v>
+      </c>
+      <c r="V6" t="str">
+        <v>Pacific Biologics Co</v>
+      </c>
+      <c r="W6" t="str">
+        <v>China</v>
+      </c>
+      <c r="X6">
+        <v>30000</v>
+      </c>
+      <c r="Y6" t="str">
+        <v>car-h</v>
+      </c>
+      <c r="Z6" t="str">
+        <v>Global Air Freight</v>
+      </c>
+      <c r="AA6" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="AB6">
+        <v>75</v>
+      </c>
+      <c r="AC6">
+        <v>63</v>
+      </c>
+      <c r="AD6" t="str">
+        <v>loc-air-lhr</v>
+      </c>
+      <c r="AE6" t="str">
+        <v>Heathrow Air Cargo Hub</v>
+      </c>
+      <c r="AF6" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG6" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="AH6">
+        <v>51.47</v>
+      </c>
+      <c r="AI6">
+        <v>-0.4543</v>
+      </c>
+      <c r="AJ6" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK6" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL6" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM6" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN6">
+        <v>33.749</v>
+      </c>
+      <c r="AO6">
+        <v>-84.388</v>
+      </c>
+      <c r="AP6">
+        <v>5</v>
+      </c>
+      <c r="AQ6">
+        <v>6</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>2</v>
+      </c>
+      <c r="AT6" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="str">
+        <v/>
+      </c>
+      <c r="AW6" t="str">
+        <v/>
+      </c>
+      <c r="AX6" t="str">
+        <v/>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>1</v>
+      </c>
+      <c r="BA6">
+        <v>1</v>
+      </c>
+      <c r="BB6">
+        <v>1</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH6" t="str">
+        <v/>
+      </c>
+      <c r="BI6" t="str">
+        <v/>
+      </c>
+      <c r="BJ6" t="str">
+        <v/>
+      </c>
+      <c r="BK6" t="str">
+        <v/>
+      </c>
+      <c r="BL6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>SHP-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C7" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>1906</v>
+      </c>
+      <c r="F7" t="str">
+        <v>2026-06-10T12:00:00.000Z</v>
+      </c>
+      <c r="G7" t="str">
+        <v>2026-06-05T12:00:00.000Z</v>
+      </c>
+      <c r="H7" t="str">
+        <v>2026-06-05T12:00:00.000Z</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L7" t="str">
+        <v>prod-omeprazole</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Omeprazole Capsules</v>
+      </c>
+      <c r="N7" t="str">
+        <v>Gastrointestinal</v>
+      </c>
+      <c r="O7" t="str">
+        <v>Ambient 15–25°C</v>
+      </c>
+      <c r="P7">
+        <v>15</v>
+      </c>
+      <c r="Q7">
+        <v>25</v>
+      </c>
+      <c r="R7" t="str">
+        <v>03000000000093</v>
+      </c>
+      <c r="S7" t="str">
+        <v>BN-2026-013</v>
+      </c>
+      <c r="T7" t="str">
+        <v>2026-05-31T12:00:00.000Z</v>
+      </c>
+      <c r="U7" t="str">
+        <v>2028-01-27T12:00:00.000Z</v>
+      </c>
+      <c r="V7" t="str">
+        <v>EuroPharma Manufacturing</v>
+      </c>
+      <c r="W7" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="X7">
+        <v>39000</v>
+      </c>
+      <c r="Y7" t="str">
+        <v>car-e</v>
+      </c>
+      <c r="Z7" t="str">
+        <v>Pacific Maritime</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="AB7">
+        <v>75</v>
+      </c>
+      <c r="AC7">
+        <v>80</v>
+      </c>
+      <c r="AD7" t="str">
+        <v>loc-port-rotterdam</v>
+      </c>
+      <c r="AE7" t="str">
+        <v>Port of Rotterdam</v>
+      </c>
+      <c r="AF7" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG7" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="AH7">
+        <v>51.9496</v>
+      </c>
+      <c r="AI7">
+        <v>4.1453</v>
+      </c>
+      <c r="AJ7" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK7" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL7" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM7" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN7">
+        <v>40.7903</v>
+      </c>
+      <c r="AO7">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP7">
+        <v>6</v>
+      </c>
+      <c r="AQ7">
+        <v>6</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>2</v>
+      </c>
+      <c r="AT7" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="str">
+        <v/>
+      </c>
+      <c r="AW7" t="str">
+        <v/>
+      </c>
+      <c r="AX7" t="str">
+        <v/>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="str">
+        <v>North Atlantic Storm System | Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH7" t="str">
+        <v/>
+      </c>
+      <c r="BI7" t="str">
+        <v/>
+      </c>
+      <c r="BJ7" t="str">
+        <v/>
+      </c>
+      <c r="BK7" t="str">
+        <v/>
+      </c>
+      <c r="BL7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>SHP-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>CUSTOMS_HOLD</v>
+      </c>
+      <c r="C8" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="D8">
+        <v>13</v>
+      </c>
+      <c r="E8">
+        <v>472</v>
+      </c>
+      <c r="F8" t="str">
+        <v>2026-06-11T12:00:00.000Z</v>
+      </c>
+      <c r="G8" t="str">
+        <v>2026-06-29T12:00:00.000Z</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L8" t="str">
+        <v>prod-flu</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Influenza Vaccine</v>
+      </c>
+      <c r="N8" t="str">
+        <v>Vaccine</v>
+      </c>
+      <c r="O8" t="str">
+        <v>Cold chain 2–8°C</v>
+      </c>
+      <c r="P8">
+        <v>2</v>
+      </c>
+      <c r="Q8">
+        <v>8</v>
+      </c>
+      <c r="R8" t="str">
+        <v>03000000000048</v>
+      </c>
+      <c r="S8" t="str">
+        <v>BN-2026-003</v>
+      </c>
+      <c r="T8" t="str">
+        <v>2026-05-03T12:00:00.000Z</v>
+      </c>
+      <c r="U8" t="str">
+        <v>2027-06-08T12:00:00.000Z</v>
+      </c>
+      <c r="V8" t="str">
+        <v>BioNTech Marburg GmbH</v>
+      </c>
+      <c r="W8" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="X8">
+        <v>36000</v>
+      </c>
+      <c r="Y8" t="str">
+        <v>car-a</v>
+      </c>
+      <c r="Z8" t="str">
+        <v>Atlantic Ocean Lines</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="AB8">
+        <v>100</v>
+      </c>
+      <c r="AC8">
+        <v>66</v>
+      </c>
+      <c r="AD8" t="str">
+        <v>loc-port-shanghai</v>
+      </c>
+      <c r="AE8" t="str">
+        <v>Port of Shanghai</v>
+      </c>
+      <c r="AF8" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG8" t="str">
+        <v>China</v>
+      </c>
+      <c r="AH8">
+        <v>31.2304</v>
+      </c>
+      <c r="AI8">
+        <v>121.4737</v>
+      </c>
+      <c r="AJ8" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK8" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL8" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM8" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN8">
+        <v>40.7903</v>
+      </c>
+      <c r="AO8">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP8">
+        <v>6</v>
+      </c>
+      <c r="AQ8">
+        <v>6</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>2</v>
+      </c>
+      <c r="AT8" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU8">
+        <v>113</v>
+      </c>
+      <c r="AV8">
+        <v>2.5</v>
+      </c>
+      <c r="AW8">
+        <v>6.8</v>
+      </c>
+      <c r="AX8">
+        <v>5</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>1</v>
+      </c>
+      <c r="BA8">
+        <v>1</v>
+      </c>
+      <c r="BB8">
+        <v>1</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="str">
+        <v>North Atlantic Storm System | Customs Congestion — Newark | Heatwave — US Northeast | Port Congestion — Los Angeles</v>
+      </c>
+      <c r="BH8" t="str">
+        <v/>
+      </c>
+      <c r="BI8" t="str">
+        <v/>
+      </c>
+      <c r="BJ8" t="str">
+        <v/>
+      </c>
+      <c r="BK8" t="str">
+        <v/>
+      </c>
+      <c r="BL8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>SHP-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>DELAYED</v>
+      </c>
+      <c r="C9" t="str">
+        <v>TRUCK</v>
+      </c>
+      <c r="D9">
+        <v>60</v>
+      </c>
+      <c r="E9">
+        <v>658</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2026-06-17T12:00:00.000Z</v>
+      </c>
+      <c r="G9" t="str">
+        <v>2026-07-04T12:00:00.000Z</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L9" t="str">
+        <v>prod-atorva</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Atorvastatin Tablets</v>
+      </c>
+      <c r="N9" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="O9" t="str">
+        <v>Ambient 15–30°C</v>
+      </c>
+      <c r="P9">
+        <v>15</v>
+      </c>
+      <c r="Q9">
+        <v>30</v>
+      </c>
+      <c r="R9" t="str">
+        <v>03000000000062</v>
+      </c>
+      <c r="S9" t="str">
+        <v>BN-2026-004</v>
+      </c>
+      <c r="T9" t="str">
+        <v>2026-04-10T12:00:00.000Z</v>
+      </c>
+      <c r="U9" t="str">
+        <v>2027-11-12T12:00:00.000Z</v>
+      </c>
+      <c r="V9" t="str">
+        <v>Atlantic Pharmaceuticals</v>
+      </c>
+      <c r="W9" t="str">
+        <v>United States</v>
+      </c>
+      <c r="X9">
+        <v>20000</v>
+      </c>
+      <c r="Y9" t="str">
+        <v>car-f</v>
+      </c>
+      <c r="Z9" t="str">
+        <v>EuroRail Logistics</v>
+      </c>
+      <c r="AA9" t="str">
+        <v>RAIL | TRUCK</v>
+      </c>
+      <c r="AB9">
+        <v>100</v>
+      </c>
+      <c r="AC9">
+        <v>62</v>
+      </c>
+      <c r="AD9" t="str">
+        <v>loc-dc-chicago</v>
+      </c>
+      <c r="AE9" t="str">
+        <v>Midwest Distribution Center — Chicago</v>
+      </c>
+      <c r="AF9" t="str">
+        <v>DC</v>
+      </c>
+      <c r="AG9" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AH9">
+        <v>41.8781</v>
+      </c>
+      <c r="AI9">
+        <v>-87.6298</v>
+      </c>
+      <c r="AJ9" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK9" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL9" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM9" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN9">
+        <v>33.749</v>
+      </c>
+      <c r="AO9">
+        <v>-84.388</v>
+      </c>
+      <c r="AP9">
+        <v>3</v>
+      </c>
+      <c r="AQ9">
+        <v>6</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>2</v>
+      </c>
+      <c r="AT9" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="str">
+        <v/>
+      </c>
+      <c r="AW9" t="str">
+        <v/>
+      </c>
+      <c r="AX9" t="str">
+        <v/>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>1</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>1</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH9" t="str">
+        <v/>
+      </c>
+      <c r="BI9" t="str">
+        <v/>
+      </c>
+      <c r="BJ9" t="str">
+        <v/>
+      </c>
+      <c r="BK9" t="str">
+        <v/>
+      </c>
+      <c r="BL9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SHP-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>IN_TRANSIT</v>
+      </c>
+      <c r="C10" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>2396</v>
+      </c>
+      <c r="F10" t="str">
+        <v>2026-06-20T12:00:00.000Z</v>
+      </c>
+      <c r="G10" t="str">
+        <v>2026-06-28T12:00:00.000Z</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L10" t="str">
+        <v>prod-omeprazole</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Omeprazole Capsules</v>
+      </c>
+      <c r="N10" t="str">
+        <v>Gastrointestinal</v>
+      </c>
+      <c r="O10" t="str">
+        <v>Ambient 15–25°C</v>
+      </c>
+      <c r="P10">
+        <v>15</v>
+      </c>
+      <c r="Q10">
+        <v>25</v>
+      </c>
+      <c r="R10" t="str">
+        <v>03000000000093</v>
+      </c>
+      <c r="S10" t="str">
+        <v>BN-2026-013</v>
+      </c>
+      <c r="T10" t="str">
+        <v>2026-05-31T12:00:00.000Z</v>
+      </c>
+      <c r="U10" t="str">
+        <v>2028-01-27T12:00:00.000Z</v>
+      </c>
+      <c r="V10" t="str">
+        <v>EuroPharma Manufacturing</v>
+      </c>
+      <c r="W10" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="X10">
+        <v>39000</v>
+      </c>
+      <c r="Y10" t="str">
+        <v>car-g</v>
+      </c>
+      <c r="Z10" t="str">
+        <v>ABC Logistics</v>
+      </c>
+      <c r="AA10" t="str">
+        <v>TRUCK | AIR</v>
+      </c>
+      <c r="AB10">
+        <v>100</v>
+      </c>
+      <c r="AC10">
+        <v>81</v>
+      </c>
+      <c r="AD10" t="str">
+        <v>loc-air-lhr</v>
+      </c>
+      <c r="AE10" t="str">
+        <v>Heathrow Air Cargo Hub</v>
+      </c>
+      <c r="AF10" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG10" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="AH10">
+        <v>51.47</v>
+      </c>
+      <c r="AI10">
+        <v>-0.4543</v>
+      </c>
+      <c r="AJ10" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK10" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL10" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM10" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN10">
+        <v>33.749</v>
+      </c>
+      <c r="AO10">
+        <v>-84.388</v>
+      </c>
+      <c r="AP10">
+        <v>5</v>
+      </c>
+      <c r="AQ10">
+        <v>6</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>2</v>
+      </c>
+      <c r="AT10" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="str">
+        <v/>
+      </c>
+      <c r="AW10" t="str">
+        <v/>
+      </c>
+      <c r="AX10" t="str">
+        <v/>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH10" t="str">
+        <v/>
+      </c>
+      <c r="BI10" t="str">
+        <v/>
+      </c>
+      <c r="BJ10" t="str">
+        <v/>
+      </c>
+      <c r="BK10" t="str">
+        <v/>
+      </c>
+      <c r="BL10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SHP-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C11" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>1634</v>
+      </c>
+      <c r="F11" t="str">
+        <v>2026-06-15T12:00:00.000Z</v>
+      </c>
+      <c r="G11" t="str">
+        <v>2026-06-23T02:00:00.000Z</v>
+      </c>
+      <c r="H11" t="str">
+        <v>2026-06-23T12:00:00.000Z</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L11" t="str">
+        <v>prod-metformin</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Metformin Tablets</v>
+      </c>
+      <c r="N11" t="str">
+        <v>Antidiabetic</v>
+      </c>
+      <c r="O11" t="str">
+        <v>Ambient 15–30°C</v>
+      </c>
+      <c r="P11">
+        <v>15</v>
+      </c>
+      <c r="Q11">
+        <v>30</v>
+      </c>
+      <c r="R11" t="str">
+        <v>03000000000079</v>
+      </c>
+      <c r="S11" t="str">
+        <v>BN-2026-011</v>
+      </c>
+      <c r="T11" t="str">
+        <v>2026-03-09T12:00:00.000Z</v>
+      </c>
+      <c r="U11" t="str">
+        <v>2026-12-28T12:00:00.000Z</v>
+      </c>
+      <c r="V11" t="str">
+        <v>Generic Pharma Mumbai Ltd</v>
+      </c>
+      <c r="W11" t="str">
+        <v>India</v>
+      </c>
+      <c r="X11">
+        <v>24000</v>
+      </c>
+      <c r="Y11" t="str">
+        <v>car-e</v>
+      </c>
+      <c r="Z11" t="str">
+        <v>Pacific Maritime</v>
+      </c>
+      <c r="AA11" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="AB11">
+        <v>75</v>
+      </c>
+      <c r="AC11">
+        <v>80</v>
+      </c>
+      <c r="AD11" t="str">
+        <v>loc-port-rotterdam</v>
+      </c>
+      <c r="AE11" t="str">
+        <v>Port of Rotterdam</v>
+      </c>
+      <c r="AF11" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG11" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="AH11">
+        <v>51.9496</v>
+      </c>
+      <c r="AI11">
+        <v>4.1453</v>
+      </c>
+      <c r="AJ11" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK11" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL11" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM11" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN11">
+        <v>33.749</v>
+      </c>
+      <c r="AO11">
+        <v>-84.388</v>
+      </c>
+      <c r="AP11">
+        <v>6</v>
+      </c>
+      <c r="AQ11">
+        <v>6</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>2</v>
+      </c>
+      <c r="AT11" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="str">
+        <v/>
+      </c>
+      <c r="AW11" t="str">
+        <v/>
+      </c>
+      <c r="AX11" t="str">
+        <v/>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="str">
+        <v>North Atlantic Storm System | Customs Congestion — Newark | Heatwave — US Northeast | Port Congestion — Los Angeles</v>
+      </c>
+      <c r="BH11" t="str">
+        <v/>
+      </c>
+      <c r="BI11" t="str">
+        <v/>
+      </c>
+      <c r="BJ11" t="str">
+        <v/>
+      </c>
+      <c r="BK11" t="str">
+        <v/>
+      </c>
+      <c r="BL11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SHP-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C12" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D12">
+        <v>21</v>
+      </c>
+      <c r="E12">
+        <v>2218</v>
+      </c>
+      <c r="F12" t="str">
+        <v>2026-06-21T12:00:00.000Z</v>
+      </c>
+      <c r="G12" t="str">
+        <v>2026-06-04T15:00:00.000Z</v>
+      </c>
+      <c r="H12" t="str">
+        <v>2026-06-05T12:00:00.000Z</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L12" t="str">
+        <v>prod-atorva</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Atorvastatin Tablets</v>
+      </c>
+      <c r="N12" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="O12" t="str">
+        <v>Ambient 15–30°C</v>
+      </c>
+      <c r="P12">
+        <v>15</v>
+      </c>
+      <c r="Q12">
+        <v>30</v>
+      </c>
+      <c r="R12" t="str">
+        <v>03000000000062</v>
+      </c>
+      <c r="S12" t="str">
+        <v>BN-2026-004</v>
+      </c>
+      <c r="T12" t="str">
+        <v>2026-04-10T12:00:00.000Z</v>
+      </c>
+      <c r="U12" t="str">
+        <v>2027-11-12T12:00:00.000Z</v>
+      </c>
+      <c r="V12" t="str">
+        <v>Atlantic Pharmaceuticals</v>
+      </c>
+      <c r="W12" t="str">
+        <v>United States</v>
+      </c>
+      <c r="X12">
+        <v>20000</v>
+      </c>
+      <c r="Y12" t="str">
+        <v>car-c</v>
+      </c>
+      <c r="Z12" t="str">
+        <v>SkyCargo Air</v>
+      </c>
+      <c r="AA12" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="AB12">
+        <v>33</v>
+      </c>
+      <c r="AC12">
+        <v>48</v>
+      </c>
+      <c r="AD12" t="str">
+        <v>loc-air-fra</v>
+      </c>
+      <c r="AE12" t="str">
+        <v>Frankfurt Air Cargo Hub</v>
+      </c>
+      <c r="AF12" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG12" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH12">
+        <v>50.0379</v>
+      </c>
+      <c r="AI12">
+        <v>8.5622</v>
+      </c>
+      <c r="AJ12" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK12" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL12" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM12" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN12">
+        <v>40.7903</v>
+      </c>
+      <c r="AO12">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP12">
+        <v>5</v>
+      </c>
+      <c r="AQ12">
+        <v>6</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>2</v>
+      </c>
+      <c r="AT12" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="str">
+        <v/>
+      </c>
+      <c r="AW12" t="str">
+        <v/>
+      </c>
+      <c r="AX12" t="str">
+        <v/>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH12" t="str">
+        <v/>
+      </c>
+      <c r="BI12" t="str">
+        <v/>
+      </c>
+      <c r="BJ12" t="str">
+        <v/>
+      </c>
+      <c r="BK12" t="str">
+        <v/>
+      </c>
+      <c r="BL12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>SHP-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>IN_TRANSIT</v>
+      </c>
+      <c r="C13" t="str">
+        <v>TRUCK</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>728</v>
+      </c>
+      <c r="F13" t="str">
+        <v>2026-06-22T12:00:00.000Z</v>
+      </c>
+      <c r="G13" t="str">
+        <v>2026-07-01T12:00:00.000Z</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L13" t="str">
+        <v>prod-salbutamol</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Salbutamol Inhaler</v>
+      </c>
+      <c r="N13" t="str">
+        <v>Respiratory</v>
+      </c>
+      <c r="O13" t="str">
+        <v>Controlled room 15–25°C</v>
+      </c>
+      <c r="P13">
+        <v>15</v>
+      </c>
+      <c r="Q13">
+        <v>25</v>
+      </c>
+      <c r="R13" t="str">
+        <v>03000000000109</v>
+      </c>
+      <c r="S13" t="str">
+        <v>BN-2026-005</v>
+      </c>
+      <c r="T13" t="str">
+        <v>2026-02-01T12:00:00.000Z</v>
+      </c>
+      <c r="U13" t="str">
+        <v>2027-03-21T12:00:00.000Z</v>
+      </c>
+      <c r="V13" t="str">
+        <v>BioNTech Marburg GmbH</v>
+      </c>
+      <c r="W13" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="X13">
+        <v>5000</v>
+      </c>
+      <c r="Y13" t="str">
+        <v>car-f</v>
+      </c>
+      <c r="Z13" t="str">
+        <v>EuroRail Logistics</v>
+      </c>
+      <c r="AA13" t="str">
+        <v>RAIL | TRUCK</v>
+      </c>
+      <c r="AB13">
+        <v>100</v>
+      </c>
+      <c r="AC13">
+        <v>62</v>
+      </c>
+      <c r="AD13" t="str">
+        <v>loc-dc-chicago</v>
+      </c>
+      <c r="AE13" t="str">
+        <v>Midwest Distribution Center — Chicago</v>
+      </c>
+      <c r="AF13" t="str">
+        <v>DC</v>
+      </c>
+      <c r="AG13" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AH13">
+        <v>41.8781</v>
+      </c>
+      <c r="AI13">
+        <v>-87.6298</v>
+      </c>
+      <c r="AJ13" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK13" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL13" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM13" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN13">
+        <v>33.749</v>
+      </c>
+      <c r="AO13">
+        <v>-84.388</v>
+      </c>
+      <c r="AP13">
+        <v>3</v>
+      </c>
+      <c r="AQ13">
+        <v>7</v>
+      </c>
+      <c r="AR13">
+        <v>2</v>
+      </c>
+      <c r="AS13">
+        <v>2</v>
+      </c>
+      <c r="AT13" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="str">
+        <v/>
+      </c>
+      <c r="AW13" t="str">
+        <v/>
+      </c>
+      <c r="AX13" t="str">
+        <v/>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>2</v>
+      </c>
+      <c r="BA13">
+        <v>2</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>1</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>1</v>
+      </c>
+      <c r="BG13" t="str">
+        <v/>
+      </c>
+      <c r="BH13" t="str">
+        <v>RCL-2025-014</v>
+      </c>
+      <c r="BI13" t="str">
+        <v>CLOSED</v>
+      </c>
+      <c r="BJ13">
+        <v>5200</v>
+      </c>
+      <c r="BK13">
+        <v>5200</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>SHP-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>DELAYED</v>
+      </c>
+      <c r="C14" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D14">
+        <v>53</v>
+      </c>
+      <c r="E14">
+        <v>507</v>
+      </c>
+      <c r="F14" t="str">
+        <v>2026-06-17T12:00:00.000Z</v>
+      </c>
+      <c r="G14" t="str">
+        <v>2026-07-05T12:00:00.000Z</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L14" t="str">
+        <v>prod-metformin</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Metformin Tablets</v>
+      </c>
+      <c r="N14" t="str">
+        <v>Antidiabetic</v>
+      </c>
+      <c r="O14" t="str">
+        <v>Ambient 15–30°C</v>
+      </c>
+      <c r="P14">
+        <v>15</v>
+      </c>
+      <c r="Q14">
+        <v>30</v>
+      </c>
+      <c r="R14" t="str">
+        <v>03000000000079</v>
+      </c>
+      <c r="S14" t="str">
+        <v>BN-2026-011</v>
+      </c>
+      <c r="T14" t="str">
+        <v>2026-03-09T12:00:00.000Z</v>
+      </c>
+      <c r="U14" t="str">
+        <v>2026-12-28T12:00:00.000Z</v>
+      </c>
+      <c r="V14" t="str">
+        <v>Generic Pharma Mumbai Ltd</v>
+      </c>
+      <c r="W14" t="str">
+        <v>India</v>
+      </c>
+      <c r="X14">
+        <v>24000</v>
+      </c>
+      <c r="Y14" t="str">
+        <v>car-g</v>
+      </c>
+      <c r="Z14" t="str">
+        <v>ABC Logistics</v>
+      </c>
+      <c r="AA14" t="str">
+        <v>TRUCK | AIR</v>
+      </c>
+      <c r="AB14">
+        <v>100</v>
+      </c>
+      <c r="AC14">
+        <v>81</v>
+      </c>
+      <c r="AD14" t="str">
+        <v>loc-air-fra</v>
+      </c>
+      <c r="AE14" t="str">
+        <v>Frankfurt Air Cargo Hub</v>
+      </c>
+      <c r="AF14" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG14" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH14">
+        <v>50.0379</v>
+      </c>
+      <c r="AI14">
+        <v>8.5622</v>
+      </c>
+      <c r="AJ14" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK14" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL14" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM14" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN14">
+        <v>40.7903</v>
+      </c>
+      <c r="AO14">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP14">
+        <v>5</v>
+      </c>
+      <c r="AQ14">
+        <v>6</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>2</v>
+      </c>
+      <c r="AT14" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="str">
+        <v/>
+      </c>
+      <c r="AW14" t="str">
+        <v/>
+      </c>
+      <c r="AX14" t="str">
+        <v/>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>1</v>
+      </c>
+      <c r="BA14">
+        <v>1</v>
+      </c>
+      <c r="BB14">
+        <v>1</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH14" t="str">
+        <v/>
+      </c>
+      <c r="BI14" t="str">
+        <v/>
+      </c>
+      <c r="BJ14" t="str">
+        <v/>
+      </c>
+      <c r="BK14" t="str">
+        <v/>
+      </c>
+      <c r="BL14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>SHP-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C15" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>2140</v>
+      </c>
+      <c r="F15" t="str">
+        <v>2026-05-22T12:00:00.000Z</v>
+      </c>
+      <c r="G15" t="str">
+        <v>2026-06-17T12:00:00.000Z</v>
+      </c>
+      <c r="H15" t="str">
+        <v>2026-06-17T12:00:00.000Z</v>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L15" t="str">
+        <v>prod-mab</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Monoclonal Antibody Infusion</v>
+      </c>
+      <c r="N15" t="str">
+        <v>Biologic (Oncology)</v>
+      </c>
+      <c r="O15" t="str">
+        <v>Cold chain 2–8°C</v>
+      </c>
+      <c r="P15">
+        <v>2</v>
+      </c>
+      <c r="Q15">
+        <v>8</v>
+      </c>
+      <c r="R15" t="str">
+        <v>03000000000031</v>
+      </c>
+      <c r="S15" t="str">
+        <v>BN-2026-017</v>
+      </c>
+      <c r="T15" t="str">
+        <v>2026-04-26T12:00:00.000Z</v>
+      </c>
+      <c r="U15" t="str">
+        <v>2027-07-18T12:00:00.000Z</v>
+      </c>
+      <c r="V15" t="str">
+        <v>EuroPharma Manufacturing</v>
+      </c>
+      <c r="W15" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="X15">
+        <v>32000</v>
+      </c>
+      <c r="Y15" t="str">
+        <v>car-a</v>
+      </c>
+      <c r="Z15" t="str">
+        <v>Atlantic Ocean Lines</v>
+      </c>
+      <c r="AA15" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="AB15">
+        <v>100</v>
+      </c>
+      <c r="AC15">
+        <v>66</v>
+      </c>
+      <c r="AD15" t="str">
+        <v>loc-port-hamburg</v>
+      </c>
+      <c r="AE15" t="str">
+        <v>Port of Hamburg</v>
+      </c>
+      <c r="AF15" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG15" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH15">
+        <v>53.5413</v>
+      </c>
+      <c r="AI15">
+        <v>9.9326</v>
+      </c>
+      <c r="AJ15" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK15" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL15" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM15" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN15">
+        <v>33.749</v>
+      </c>
+      <c r="AO15">
+        <v>-84.388</v>
+      </c>
+      <c r="AP15">
+        <v>6</v>
+      </c>
+      <c r="AQ15">
+        <v>6</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>2</v>
+      </c>
+      <c r="AT15" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU15">
+        <v>209</v>
+      </c>
+      <c r="AV15">
+        <v>3.3</v>
+      </c>
+      <c r="AW15">
+        <v>9.6</v>
+      </c>
+      <c r="AX15">
+        <v>5.1</v>
+      </c>
+      <c r="AY15">
+        <v>3</v>
+      </c>
+      <c r="AZ15">
+        <v>2</v>
+      </c>
+      <c r="BA15">
+        <v>1</v>
+      </c>
+      <c r="BB15">
+        <v>0</v>
+      </c>
+      <c r="BC15">
+        <v>1</v>
+      </c>
+      <c r="BD15">
+        <v>1</v>
+      </c>
+      <c r="BE15">
+        <v>0</v>
+      </c>
+      <c r="BF15">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="str">
+        <v>North Atlantic Storm System | Customs Congestion — Newark | Heatwave — US Northeast | Fog — Port of Hamburg</v>
+      </c>
+      <c r="BH15" t="str">
+        <v/>
+      </c>
+      <c r="BI15" t="str">
+        <v/>
+      </c>
+      <c r="BJ15" t="str">
+        <v/>
+      </c>
+      <c r="BK15" t="str">
+        <v/>
+      </c>
+      <c r="BL15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SHP-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C16" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D16">
+        <v>17</v>
+      </c>
+      <c r="E16">
+        <v>2318</v>
+      </c>
+      <c r="F16" t="str">
+        <v>2026-06-22T12:00:00.000Z</v>
+      </c>
+      <c r="G16" t="str">
+        <v>2026-06-13T19:00:00.000Z</v>
+      </c>
+      <c r="H16" t="str">
+        <v>2026-06-14T12:00:00.000Z</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L16" t="str">
+        <v>prod-salbutamol</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Salbutamol Inhaler</v>
+      </c>
+      <c r="N16" t="str">
+        <v>Respiratory</v>
+      </c>
+      <c r="O16" t="str">
+        <v>Controlled room 15–25°C</v>
+      </c>
+      <c r="P16">
+        <v>15</v>
+      </c>
+      <c r="Q16">
+        <v>25</v>
+      </c>
+      <c r="R16" t="str">
+        <v>03000000000109</v>
+      </c>
+      <c r="S16" t="str">
+        <v>BN-2026-005</v>
+      </c>
+      <c r="T16" t="str">
+        <v>2026-02-01T12:00:00.000Z</v>
+      </c>
+      <c r="U16" t="str">
+        <v>2027-03-21T12:00:00.000Z</v>
+      </c>
+      <c r="V16" t="str">
+        <v>BioNTech Marburg GmbH</v>
+      </c>
+      <c r="W16" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="X16">
+        <v>5000</v>
+      </c>
+      <c r="Y16" t="str">
+        <v>car-h</v>
+      </c>
+      <c r="Z16" t="str">
+        <v>Global Air Freight</v>
+      </c>
+      <c r="AA16" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="AB16">
+        <v>75</v>
+      </c>
+      <c r="AC16">
+        <v>63</v>
+      </c>
+      <c r="AD16" t="str">
+        <v>loc-air-fra</v>
+      </c>
+      <c r="AE16" t="str">
+        <v>Frankfurt Air Cargo Hub</v>
+      </c>
+      <c r="AF16" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG16" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH16">
+        <v>50.0379</v>
+      </c>
+      <c r="AI16">
+        <v>8.5622</v>
+      </c>
+      <c r="AJ16" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK16" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL16" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM16" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN16">
+        <v>40.7903</v>
+      </c>
+      <c r="AO16">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP16">
+        <v>5</v>
+      </c>
+      <c r="AQ16">
+        <v>6</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>2</v>
+      </c>
+      <c r="AT16" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="str">
+        <v/>
+      </c>
+      <c r="AW16" t="str">
+        <v/>
+      </c>
+      <c r="AX16" t="str">
+        <v/>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <v>0</v>
+      </c>
+      <c r="BB16">
+        <v>0</v>
+      </c>
+      <c r="BC16">
+        <v>0</v>
+      </c>
+      <c r="BD16">
+        <v>0</v>
+      </c>
+      <c r="BE16">
+        <v>0</v>
+      </c>
+      <c r="BF16">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH16" t="str">
+        <v>RCL-2025-014</v>
+      </c>
+      <c r="BI16" t="str">
+        <v>CLOSED</v>
+      </c>
+      <c r="BJ16">
+        <v>5200</v>
+      </c>
+      <c r="BK16">
+        <v>5200</v>
+      </c>
+      <c r="BL16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SHP-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>CUSTOMS_HOLD</v>
+      </c>
+      <c r="C17" t="str">
+        <v>TRUCK</v>
+      </c>
+      <c r="D17">
+        <v>34</v>
+      </c>
+      <c r="E17">
+        <v>1485</v>
+      </c>
+      <c r="F17" t="str">
+        <v>2026-06-21T12:00:00.000Z</v>
+      </c>
+      <c r="G17" t="str">
+        <v>2026-07-03T12:00:00.000Z</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L17" t="str">
+        <v>prod-amox</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Amoxicillin Capsules</v>
+      </c>
+      <c r="N17" t="str">
+        <v>Antibiotic</v>
+      </c>
+      <c r="O17" t="str">
+        <v>Ambient 15–25°C</v>
+      </c>
+      <c r="P17">
+        <v>15</v>
+      </c>
+      <c r="Q17">
+        <v>25</v>
+      </c>
+      <c r="R17" t="str">
+        <v>03000000000055</v>
+      </c>
+      <c r="S17" t="str">
+        <v>BN-2026-020</v>
+      </c>
+      <c r="T17" t="str">
+        <v>2026-02-10T12:00:00.000Z</v>
+      </c>
+      <c r="U17" t="str">
+        <v>2027-10-07T12:00:00.000Z</v>
+      </c>
+      <c r="V17" t="str">
+        <v>BioNTech Marburg GmbH</v>
+      </c>
+      <c r="W17" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="X17">
+        <v>35000</v>
+      </c>
+      <c r="Y17" t="str">
+        <v>car-f</v>
+      </c>
+      <c r="Z17" t="str">
+        <v>EuroRail Logistics</v>
+      </c>
+      <c r="AA17" t="str">
+        <v>RAIL | TRUCK</v>
+      </c>
+      <c r="AB17">
+        <v>100</v>
+      </c>
+      <c r="AC17">
+        <v>62</v>
+      </c>
+      <c r="AD17" t="str">
+        <v>loc-3pl-nj</v>
+      </c>
+      <c r="AE17" t="str">
+        <v>3PL Warehouse — Edison NJ</v>
+      </c>
+      <c r="AF17" t="str">
+        <v>3PL</v>
+      </c>
+      <c r="AG17" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AH17">
+        <v>40.5187</v>
+      </c>
+      <c r="AI17">
+        <v>-74.4121</v>
+      </c>
+      <c r="AJ17" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK17" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL17" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM17" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN17">
+        <v>33.749</v>
+      </c>
+      <c r="AO17">
+        <v>-84.388</v>
+      </c>
+      <c r="AP17">
+        <v>3</v>
+      </c>
+      <c r="AQ17">
+        <v>6</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>2</v>
+      </c>
+      <c r="AT17" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="str">
+        <v/>
+      </c>
+      <c r="AW17" t="str">
+        <v/>
+      </c>
+      <c r="AX17" t="str">
+        <v/>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>1</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>1</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH17" t="str">
+        <v/>
+      </c>
+      <c r="BI17" t="str">
+        <v/>
+      </c>
+      <c r="BJ17" t="str">
+        <v/>
+      </c>
+      <c r="BK17" t="str">
+        <v/>
+      </c>
+      <c r="BL17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SHP-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>IN_TRANSIT</v>
+      </c>
+      <c r="C18" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>652</v>
+      </c>
+      <c r="F18" t="str">
+        <v>2026-06-19T12:00:00.000Z</v>
+      </c>
+      <c r="G18" t="str">
+        <v>2026-07-07T12:00:00.000Z</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L18" t="str">
+        <v>prod-flu</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Influenza Vaccine</v>
+      </c>
+      <c r="N18" t="str">
+        <v>Vaccine</v>
+      </c>
+      <c r="O18" t="str">
+        <v>Cold chain 2–8°C</v>
+      </c>
+      <c r="P18">
+        <v>2</v>
+      </c>
+      <c r="Q18">
+        <v>8</v>
+      </c>
+      <c r="R18" t="str">
+        <v>03000000000048</v>
+      </c>
+      <c r="S18" t="str">
+        <v>BN-2026-003</v>
+      </c>
+      <c r="T18" t="str">
+        <v>2026-05-03T12:00:00.000Z</v>
+      </c>
+      <c r="U18" t="str">
+        <v>2027-06-08T12:00:00.000Z</v>
+      </c>
+      <c r="V18" t="str">
+        <v>BioNTech Marburg GmbH</v>
+      </c>
+      <c r="W18" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="X18">
+        <v>36000</v>
+      </c>
+      <c r="Y18" t="str">
+        <v>car-g</v>
+      </c>
+      <c r="Z18" t="str">
+        <v>ABC Logistics</v>
+      </c>
+      <c r="AA18" t="str">
+        <v>TRUCK | AIR</v>
+      </c>
+      <c r="AB18">
+        <v>100</v>
+      </c>
+      <c r="AC18">
+        <v>81</v>
+      </c>
+      <c r="AD18" t="str">
+        <v>loc-air-fra</v>
+      </c>
+      <c r="AE18" t="str">
+        <v>Frankfurt Air Cargo Hub</v>
+      </c>
+      <c r="AF18" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG18" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH18">
+        <v>50.0379</v>
+      </c>
+      <c r="AI18">
+        <v>8.5622</v>
+      </c>
+      <c r="AJ18" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK18" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL18" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM18" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN18">
+        <v>33.749</v>
+      </c>
+      <c r="AO18">
+        <v>-84.388</v>
+      </c>
+      <c r="AP18">
+        <v>5</v>
+      </c>
+      <c r="AQ18">
+        <v>6</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>2</v>
+      </c>
+      <c r="AT18" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU18">
+        <v>49</v>
+      </c>
+      <c r="AV18">
+        <v>3.5</v>
+      </c>
+      <c r="AW18">
+        <v>6.7</v>
+      </c>
+      <c r="AX18">
+        <v>4.8</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH18" t="str">
+        <v/>
+      </c>
+      <c r="BI18" t="str">
+        <v/>
+      </c>
+      <c r="BJ18" t="str">
+        <v/>
+      </c>
+      <c r="BK18" t="str">
+        <v/>
+      </c>
+      <c r="BL18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SHP-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C19" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>2293</v>
+      </c>
+      <c r="F19" t="str">
+        <v>2026-06-07T12:00:00.000Z</v>
+      </c>
+      <c r="G19" t="str">
+        <v>2026-06-23T12:00:00.000Z</v>
+      </c>
+      <c r="H19" t="str">
+        <v>2026-06-23T12:00:00.000Z</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L19" t="str">
+        <v>prod-salbutamol</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Salbutamol Inhaler</v>
+      </c>
+      <c r="N19" t="str">
+        <v>Respiratory</v>
+      </c>
+      <c r="O19" t="str">
+        <v>Controlled room 15–25°C</v>
+      </c>
+      <c r="P19">
+        <v>15</v>
+      </c>
+      <c r="Q19">
+        <v>25</v>
+      </c>
+      <c r="R19" t="str">
+        <v>03000000000109</v>
+      </c>
+      <c r="S19" t="str">
+        <v>BN-2026-015</v>
+      </c>
+      <c r="T19" t="str">
+        <v>2026-05-07T12:00:00.000Z</v>
+      </c>
+      <c r="U19" t="str">
+        <v>2027-05-25T12:00:00.000Z</v>
+      </c>
+      <c r="V19" t="str">
+        <v>BioNTech Marburg GmbH</v>
+      </c>
+      <c r="W19" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="X19">
+        <v>15000</v>
+      </c>
+      <c r="Y19" t="str">
+        <v>car-e</v>
+      </c>
+      <c r="Z19" t="str">
+        <v>Pacific Maritime</v>
+      </c>
+      <c r="AA19" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="AB19">
+        <v>75</v>
+      </c>
+      <c r="AC19">
+        <v>80</v>
+      </c>
+      <c r="AD19" t="str">
+        <v>loc-port-shanghai</v>
+      </c>
+      <c r="AE19" t="str">
+        <v>Port of Shanghai</v>
+      </c>
+      <c r="AF19" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG19" t="str">
+        <v>China</v>
+      </c>
+      <c r="AH19">
+        <v>31.2304</v>
+      </c>
+      <c r="AI19">
+        <v>121.4737</v>
+      </c>
+      <c r="AJ19" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK19" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL19" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM19" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN19">
+        <v>40.7903</v>
+      </c>
+      <c r="AO19">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP19">
+        <v>6</v>
+      </c>
+      <c r="AQ19">
+        <v>6</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>2</v>
+      </c>
+      <c r="AT19" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="str">
+        <v/>
+      </c>
+      <c r="AW19" t="str">
+        <v/>
+      </c>
+      <c r="AX19" t="str">
+        <v/>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="str">
+        <v>North Atlantic Storm System | Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH19" t="str">
+        <v/>
+      </c>
+      <c r="BI19" t="str">
+        <v/>
+      </c>
+      <c r="BJ19" t="str">
+        <v/>
+      </c>
+      <c r="BK19" t="str">
+        <v/>
+      </c>
+      <c r="BL19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SHP-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>IN_TRANSIT</v>
+      </c>
+      <c r="C20" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>605</v>
+      </c>
+      <c r="F20" t="str">
+        <v>2026-06-18T12:00:00.000Z</v>
+      </c>
+      <c r="G20" t="str">
+        <v>2026-07-03T12:00:00.000Z</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L20" t="str">
+        <v>prod-atorva</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Atorvastatin Tablets</v>
+      </c>
+      <c r="N20" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="O20" t="str">
+        <v>Ambient 15–30°C</v>
+      </c>
+      <c r="P20">
+        <v>15</v>
+      </c>
+      <c r="Q20">
+        <v>30</v>
+      </c>
+      <c r="R20" t="str">
+        <v>03000000000062</v>
+      </c>
+      <c r="S20" t="str">
+        <v>BN-2026-002</v>
+      </c>
+      <c r="T20" t="str">
+        <v>2026-02-09T12:00:00.000Z</v>
+      </c>
+      <c r="U20" t="str">
+        <v>2026-11-01T12:00:00.000Z</v>
+      </c>
+      <c r="V20" t="str">
+        <v>Generic Pharma Mumbai Ltd</v>
+      </c>
+      <c r="W20" t="str">
+        <v>India</v>
+      </c>
+      <c r="X20">
+        <v>34000</v>
+      </c>
+      <c r="Y20" t="str">
+        <v>car-h</v>
+      </c>
+      <c r="Z20" t="str">
+        <v>Global Air Freight</v>
+      </c>
+      <c r="AA20" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="AB20">
+        <v>75</v>
+      </c>
+      <c r="AC20">
+        <v>63</v>
+      </c>
+      <c r="AD20" t="str">
+        <v>loc-air-fra</v>
+      </c>
+      <c r="AE20" t="str">
+        <v>Frankfurt Air Cargo Hub</v>
+      </c>
+      <c r="AF20" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG20" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH20">
+        <v>50.0379</v>
+      </c>
+      <c r="AI20">
+        <v>8.5622</v>
+      </c>
+      <c r="AJ20" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK20" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL20" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM20" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN20">
+        <v>40.7903</v>
+      </c>
+      <c r="AO20">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP20">
+        <v>5</v>
+      </c>
+      <c r="AQ20">
+        <v>6</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>2</v>
+      </c>
+      <c r="AT20" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="str">
+        <v/>
+      </c>
+      <c r="AW20" t="str">
+        <v/>
+      </c>
+      <c r="AX20" t="str">
+        <v/>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <v>0</v>
+      </c>
+      <c r="BC20">
+        <v>0</v>
+      </c>
+      <c r="BD20">
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <v>0</v>
+      </c>
+      <c r="BF20">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH20" t="str">
+        <v/>
+      </c>
+      <c r="BI20" t="str">
+        <v/>
+      </c>
+      <c r="BJ20" t="str">
+        <v/>
+      </c>
+      <c r="BK20" t="str">
+        <v/>
+      </c>
+      <c r="BL20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SHP-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>DELAYED</v>
+      </c>
+      <c r="C21" t="str">
+        <v>TRUCK</v>
+      </c>
+      <c r="D21">
+        <v>59</v>
+      </c>
+      <c r="E21">
+        <v>1916</v>
+      </c>
+      <c r="F21" t="str">
+        <v>2026-06-23T12:00:00.000Z</v>
+      </c>
+      <c r="G21" t="str">
+        <v>2026-07-04T12:00:00.000Z</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L21" t="str">
+        <v>prod-flu</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Influenza Vaccine</v>
+      </c>
+      <c r="N21" t="str">
+        <v>Vaccine</v>
+      </c>
+      <c r="O21" t="str">
+        <v>Cold chain 2–8°C</v>
+      </c>
+      <c r="P21">
+        <v>2</v>
+      </c>
+      <c r="Q21">
+        <v>8</v>
+      </c>
+      <c r="R21" t="str">
+        <v>03000000000048</v>
+      </c>
+      <c r="S21" t="str">
+        <v>BN-2026-008</v>
+      </c>
+      <c r="T21" t="str">
+        <v>2026-05-08T12:00:00.000Z</v>
+      </c>
+      <c r="U21" t="str">
+        <v>2027-08-04T12:00:00.000Z</v>
+      </c>
+      <c r="V21" t="str">
+        <v>BioNTech Marburg GmbH</v>
+      </c>
+      <c r="W21" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="X21">
+        <v>8000</v>
+      </c>
+      <c r="Y21" t="str">
+        <v>car-d</v>
+      </c>
+      <c r="Z21" t="str">
+        <v>TransContinental Trucking</v>
+      </c>
+      <c r="AA21" t="str">
+        <v>TRUCK</v>
+      </c>
+      <c r="AB21">
+        <v>50</v>
+      </c>
+      <c r="AC21">
+        <v>52</v>
+      </c>
+      <c r="AD21" t="str">
+        <v>loc-dc-chicago</v>
+      </c>
+      <c r="AE21" t="str">
+        <v>Midwest Distribution Center — Chicago</v>
+      </c>
+      <c r="AF21" t="str">
+        <v>DC</v>
+      </c>
+      <c r="AG21" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AH21">
+        <v>41.8781</v>
+      </c>
+      <c r="AI21">
+        <v>-87.6298</v>
+      </c>
+      <c r="AJ21" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK21" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL21" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM21" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN21">
+        <v>33.749</v>
+      </c>
+      <c r="AO21">
+        <v>-84.388</v>
+      </c>
+      <c r="AP21">
+        <v>3</v>
+      </c>
+      <c r="AQ21">
+        <v>6</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>2</v>
+      </c>
+      <c r="AT21" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU21">
+        <v>17</v>
+      </c>
+      <c r="AV21">
+        <v>3.7</v>
+      </c>
+      <c r="AW21">
+        <v>6.2</v>
+      </c>
+      <c r="AX21">
+        <v>4.8</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>1</v>
+      </c>
+      <c r="BA21">
+        <v>1</v>
+      </c>
+      <c r="BB21">
+        <v>1</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH21" t="str">
+        <v/>
+      </c>
+      <c r="BI21" t="str">
+        <v/>
+      </c>
+      <c r="BJ21" t="str">
+        <v/>
+      </c>
+      <c r="BK21" t="str">
+        <v/>
+      </c>
+      <c r="BL21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SHP-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>DELAYED</v>
+      </c>
+      <c r="C22" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D22">
+        <v>38</v>
+      </c>
+      <c r="E22">
+        <v>299</v>
+      </c>
+      <c r="F22" t="str">
+        <v>2026-06-20T12:00:00.000Z</v>
+      </c>
+      <c r="G22" t="str">
+        <v>2026-06-29T12:00:00.000Z</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L22" t="str">
+        <v>prod-insulin</v>
+      </c>
+      <c r="M22" t="str">
+        <v>Insulin Glargine Injection</v>
+      </c>
+      <c r="N22" t="str">
+        <v>Biologic (Antidiabetic)</v>
+      </c>
+      <c r="O22" t="str">
+        <v>Cold chain 2–8°C</v>
+      </c>
+      <c r="P22">
+        <v>2</v>
+      </c>
+      <c r="Q22">
+        <v>8</v>
+      </c>
+      <c r="R22" t="str">
+        <v>03000000000024</v>
+      </c>
+      <c r="S22" t="str">
+        <v>BN-2026-007</v>
+      </c>
+      <c r="T22" t="str">
+        <v>2026-04-26T12:00:00.000Z</v>
+      </c>
+      <c r="U22" t="str">
+        <v>2027-04-12T12:00:00.000Z</v>
+      </c>
+      <c r="V22" t="str">
+        <v>Atlantic Pharmaceuticals</v>
+      </c>
+      <c r="W22" t="str">
+        <v>United States</v>
+      </c>
+      <c r="X22">
+        <v>7000</v>
+      </c>
+      <c r="Y22" t="str">
+        <v>car-h</v>
+      </c>
+      <c r="Z22" t="str">
+        <v>Global Air Freight</v>
+      </c>
+      <c r="AA22" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="AB22">
+        <v>75</v>
+      </c>
+      <c r="AC22">
+        <v>63</v>
+      </c>
+      <c r="AD22" t="str">
+        <v>loc-air-lhr</v>
+      </c>
+      <c r="AE22" t="str">
+        <v>Heathrow Air Cargo Hub</v>
+      </c>
+      <c r="AF22" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG22" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="AH22">
+        <v>51.47</v>
+      </c>
+      <c r="AI22">
+        <v>-0.4543</v>
+      </c>
+      <c r="AJ22" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK22" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL22" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM22" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN22">
+        <v>40.7903</v>
+      </c>
+      <c r="AO22">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP22">
+        <v>5</v>
+      </c>
+      <c r="AQ22">
+        <v>6</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>2</v>
+      </c>
+      <c r="AT22" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU22">
+        <v>41</v>
+      </c>
+      <c r="AV22">
+        <v>3.4</v>
+      </c>
+      <c r="AW22">
+        <v>9.8</v>
+      </c>
+      <c r="AX22">
+        <v>5.5</v>
+      </c>
+      <c r="AY22">
+        <v>3</v>
+      </c>
+      <c r="AZ22">
+        <v>2</v>
+      </c>
+      <c r="BA22">
+        <v>1</v>
+      </c>
+      <c r="BB22">
+        <v>1</v>
+      </c>
+      <c r="BC22">
+        <v>1</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH22" t="str">
+        <v/>
+      </c>
+      <c r="BI22" t="str">
+        <v/>
+      </c>
+      <c r="BJ22" t="str">
+        <v/>
+      </c>
+      <c r="BK22" t="str">
+        <v/>
+      </c>
+      <c r="BL22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>SHP-022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>IN_TRANSIT</v>
+      </c>
+      <c r="C23" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>2203</v>
+      </c>
+      <c r="F23" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="G23" t="str">
+        <v>2026-06-27T12:00:00.000Z</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L23" t="str">
+        <v>prod-mab</v>
+      </c>
+      <c r="M23" t="str">
+        <v>Monoclonal Antibody Infusion</v>
+      </c>
+      <c r="N23" t="str">
+        <v>Biologic (Oncology)</v>
+      </c>
+      <c r="O23" t="str">
+        <v>Cold chain 2–8°C</v>
+      </c>
+      <c r="P23">
+        <v>2</v>
+      </c>
+      <c r="Q23">
+        <v>8</v>
+      </c>
+      <c r="R23" t="str">
+        <v>03000000000031</v>
+      </c>
+      <c r="S23" t="str">
+        <v>BN-2026-017</v>
+      </c>
+      <c r="T23" t="str">
+        <v>2026-04-26T12:00:00.000Z</v>
+      </c>
+      <c r="U23" t="str">
+        <v>2027-07-18T12:00:00.000Z</v>
+      </c>
+      <c r="V23" t="str">
+        <v>EuroPharma Manufacturing</v>
+      </c>
+      <c r="W23" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="X23">
+        <v>32000</v>
+      </c>
+      <c r="Y23" t="str">
+        <v>car-a</v>
+      </c>
+      <c r="Z23" t="str">
+        <v>Atlantic Ocean Lines</v>
+      </c>
+      <c r="AA23" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="AB23">
+        <v>100</v>
+      </c>
+      <c r="AC23">
+        <v>66</v>
+      </c>
+      <c r="AD23" t="str">
+        <v>loc-port-hamburg</v>
+      </c>
+      <c r="AE23" t="str">
+        <v>Port of Hamburg</v>
+      </c>
+      <c r="AF23" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG23" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH23">
+        <v>53.5413</v>
+      </c>
+      <c r="AI23">
+        <v>9.9326</v>
+      </c>
+      <c r="AJ23" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK23" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL23" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM23" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN23">
+        <v>33.749</v>
+      </c>
+      <c r="AO23">
+        <v>-84.388</v>
+      </c>
+      <c r="AP23">
+        <v>6</v>
+      </c>
+      <c r="AQ23">
+        <v>6</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>2</v>
+      </c>
+      <c r="AT23" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU23">
+        <v>193</v>
+      </c>
+      <c r="AV23">
+        <v>2.8</v>
+      </c>
+      <c r="AW23">
+        <v>10.6</v>
+      </c>
+      <c r="AX23">
+        <v>5.1</v>
+      </c>
+      <c r="AY23">
+        <v>2</v>
+      </c>
+      <c r="AZ23">
+        <v>2</v>
+      </c>
+      <c r="BA23">
+        <v>1</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>1</v>
+      </c>
+      <c r="BD23">
+        <v>1</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="str">
+        <v>North Atlantic Storm System | Customs Congestion — Newark | Heatwave — US Northeast | Fog — Port of Hamburg</v>
+      </c>
+      <c r="BH23" t="str">
+        <v/>
+      </c>
+      <c r="BI23" t="str">
+        <v/>
+      </c>
+      <c r="BJ23" t="str">
+        <v/>
+      </c>
+      <c r="BK23" t="str">
+        <v/>
+      </c>
+      <c r="BL23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SHP-023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C24" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>2334</v>
+      </c>
+      <c r="F24" t="str">
+        <v>2026-06-16T12:00:00.000Z</v>
+      </c>
+      <c r="G24" t="str">
+        <v>2026-06-21T12:00:00.000Z</v>
+      </c>
+      <c r="H24" t="str">
+        <v>2026-06-21T12:00:00.000Z</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L24" t="str">
+        <v>prod-ibuprofen</v>
+      </c>
+      <c r="M24" t="str">
+        <v>Ibuprofen Tablets</v>
+      </c>
+      <c r="N24" t="str">
+        <v>Analgesic</v>
+      </c>
+      <c r="O24" t="str">
+        <v>Ambient 15–25°C</v>
+      </c>
+      <c r="P24">
+        <v>15</v>
+      </c>
+      <c r="Q24">
+        <v>25</v>
+      </c>
+      <c r="R24" t="str">
+        <v>03000000000086</v>
+      </c>
+      <c r="S24" t="str">
+        <v>BN-2026-018</v>
+      </c>
+      <c r="T24" t="str">
+        <v>2026-03-20T12:00:00.000Z</v>
+      </c>
+      <c r="U24" t="str">
+        <v>2028-02-27T12:00:00.000Z</v>
+      </c>
+      <c r="V24" t="str">
+        <v>EuroPharma Manufacturing</v>
+      </c>
+      <c r="W24" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="X24">
+        <v>27000</v>
+      </c>
+      <c r="Y24" t="str">
+        <v>car-g</v>
+      </c>
+      <c r="Z24" t="str">
+        <v>ABC Logistics</v>
+      </c>
+      <c r="AA24" t="str">
+        <v>TRUCK | AIR</v>
+      </c>
+      <c r="AB24">
+        <v>100</v>
+      </c>
+      <c r="AC24">
+        <v>81</v>
+      </c>
+      <c r="AD24" t="str">
+        <v>loc-air-fra</v>
+      </c>
+      <c r="AE24" t="str">
+        <v>Frankfurt Air Cargo Hub</v>
+      </c>
+      <c r="AF24" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG24" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH24">
+        <v>50.0379</v>
+      </c>
+      <c r="AI24">
+        <v>8.5622</v>
+      </c>
+      <c r="AJ24" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK24" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL24" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM24" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN24">
+        <v>40.7903</v>
+      </c>
+      <c r="AO24">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP24">
+        <v>5</v>
+      </c>
+      <c r="AQ24">
+        <v>6</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>2</v>
+      </c>
+      <c r="AT24" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU24">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="str">
+        <v/>
+      </c>
+      <c r="AW24" t="str">
+        <v/>
+      </c>
+      <c r="AX24" t="str">
+        <v/>
+      </c>
+      <c r="AY24">
+        <v>0</v>
+      </c>
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
+        <v>0</v>
+      </c>
+      <c r="BB24">
+        <v>0</v>
+      </c>
+      <c r="BC24">
+        <v>0</v>
+      </c>
+      <c r="BD24">
+        <v>0</v>
+      </c>
+      <c r="BE24">
+        <v>0</v>
+      </c>
+      <c r="BF24">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH24" t="str">
+        <v/>
+      </c>
+      <c r="BI24" t="str">
+        <v/>
+      </c>
+      <c r="BJ24" t="str">
+        <v/>
+      </c>
+      <c r="BK24" t="str">
+        <v/>
+      </c>
+      <c r="BL24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>SHP-024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C25" t="str">
+        <v>TRUCK</v>
+      </c>
+      <c r="D25">
+        <v>14</v>
+      </c>
+      <c r="E25">
+        <v>1639</v>
+      </c>
+      <c r="F25" t="str">
+        <v>2026-06-22T12:00:00.000Z</v>
+      </c>
+      <c r="G25" t="str">
+        <v>2026-06-10T22:00:00.000Z</v>
+      </c>
+      <c r="H25" t="str">
+        <v>2026-06-11T12:00:00.000Z</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L25" t="str">
+        <v>prod-omeprazole</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Omeprazole Capsules</v>
+      </c>
+      <c r="N25" t="str">
+        <v>Gastrointestinal</v>
+      </c>
+      <c r="O25" t="str">
+        <v>Ambient 15–25°C</v>
+      </c>
+      <c r="P25">
+        <v>15</v>
+      </c>
+      <c r="Q25">
+        <v>25</v>
+      </c>
+      <c r="R25" t="str">
+        <v>03000000000093</v>
+      </c>
+      <c r="S25" t="str">
+        <v>BN-2026-016</v>
+      </c>
+      <c r="T25" t="str">
+        <v>2026-04-04T12:00:00.000Z</v>
+      </c>
+      <c r="U25" t="str">
+        <v>2026-12-31T12:00:00.000Z</v>
+      </c>
+      <c r="V25" t="str">
+        <v>Generic Pharma Mumbai Ltd</v>
+      </c>
+      <c r="W25" t="str">
+        <v>India</v>
+      </c>
+      <c r="X25">
+        <v>5000</v>
+      </c>
+      <c r="Y25" t="str">
+        <v>car-d</v>
+      </c>
+      <c r="Z25" t="str">
+        <v>TransContinental Trucking</v>
+      </c>
+      <c r="AA25" t="str">
+        <v>TRUCK</v>
+      </c>
+      <c r="AB25">
+        <v>50</v>
+      </c>
+      <c r="AC25">
+        <v>52</v>
+      </c>
+      <c r="AD25" t="str">
+        <v>loc-3pl-dallas</v>
+      </c>
+      <c r="AE25" t="str">
+        <v>3PL Warehouse — Dallas TX</v>
+      </c>
+      <c r="AF25" t="str">
+        <v>3PL</v>
+      </c>
+      <c r="AG25" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AH25">
+        <v>32.7767</v>
+      </c>
+      <c r="AI25">
+        <v>-96.797</v>
+      </c>
+      <c r="AJ25" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK25" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL25" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM25" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN25">
+        <v>40.7903</v>
+      </c>
+      <c r="AO25">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP25">
+        <v>3</v>
+      </c>
+      <c r="AQ25">
+        <v>6</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>2</v>
+      </c>
+      <c r="AT25" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="str">
+        <v/>
+      </c>
+      <c r="AW25" t="str">
+        <v/>
+      </c>
+      <c r="AX25" t="str">
+        <v/>
+      </c>
+      <c r="AY25">
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <v>0</v>
+      </c>
+      <c r="BB25">
+        <v>0</v>
+      </c>
+      <c r="BC25">
+        <v>0</v>
+      </c>
+      <c r="BD25">
+        <v>0</v>
+      </c>
+      <c r="BE25">
+        <v>0</v>
+      </c>
+      <c r="BF25">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH25" t="str">
+        <v/>
+      </c>
+      <c r="BI25" t="str">
+        <v/>
+      </c>
+      <c r="BJ25" t="str">
+        <v/>
+      </c>
+      <c r="BK25" t="str">
+        <v/>
+      </c>
+      <c r="BL25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>SHP-025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>CUSTOMS_HOLD</v>
+      </c>
+      <c r="C26" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D26">
+        <v>10</v>
+      </c>
+      <c r="E26">
+        <v>1803</v>
+      </c>
+      <c r="F26" t="str">
+        <v>2026-06-18T12:00:00.000Z</v>
+      </c>
+      <c r="G26" t="str">
+        <v>2026-07-01T12:00:00.000Z</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L26" t="str">
+        <v>prod-ibuprofen</v>
+      </c>
+      <c r="M26" t="str">
+        <v>Ibuprofen Tablets</v>
+      </c>
+      <c r="N26" t="str">
+        <v>Analgesic</v>
+      </c>
+      <c r="O26" t="str">
+        <v>Ambient 15–25°C</v>
+      </c>
+      <c r="P26">
+        <v>15</v>
+      </c>
+      <c r="Q26">
+        <v>25</v>
+      </c>
+      <c r="R26" t="str">
+        <v>03000000000086</v>
+      </c>
+      <c r="S26" t="str">
+        <v>BN-2026-018</v>
+      </c>
+      <c r="T26" t="str">
+        <v>2026-03-20T12:00:00.000Z</v>
+      </c>
+      <c r="U26" t="str">
+        <v>2028-02-27T12:00:00.000Z</v>
+      </c>
+      <c r="V26" t="str">
+        <v>EuroPharma Manufacturing</v>
+      </c>
+      <c r="W26" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="X26">
+        <v>27000</v>
+      </c>
+      <c r="Y26" t="str">
+        <v>car-h</v>
+      </c>
+      <c r="Z26" t="str">
+        <v>Global Air Freight</v>
+      </c>
+      <c r="AA26" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="AB26">
+        <v>75</v>
+      </c>
+      <c r="AC26">
+        <v>63</v>
+      </c>
+      <c r="AD26" t="str">
+        <v>loc-air-fra</v>
+      </c>
+      <c r="AE26" t="str">
+        <v>Frankfurt Air Cargo Hub</v>
+      </c>
+      <c r="AF26" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG26" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH26">
+        <v>50.0379</v>
+      </c>
+      <c r="AI26">
+        <v>8.5622</v>
+      </c>
+      <c r="AJ26" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK26" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL26" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM26" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN26">
+        <v>33.749</v>
+      </c>
+      <c r="AO26">
+        <v>-84.388</v>
+      </c>
+      <c r="AP26">
+        <v>5</v>
+      </c>
+      <c r="AQ26">
+        <v>6</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>2</v>
+      </c>
+      <c r="AT26" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU26">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="str">
+        <v/>
+      </c>
+      <c r="AW26" t="str">
+        <v/>
+      </c>
+      <c r="AX26" t="str">
+        <v/>
+      </c>
+      <c r="AY26">
+        <v>0</v>
+      </c>
+      <c r="AZ26">
+        <v>1</v>
+      </c>
+      <c r="BA26">
+        <v>0</v>
+      </c>
+      <c r="BB26">
+        <v>1</v>
+      </c>
+      <c r="BC26">
+        <v>0</v>
+      </c>
+      <c r="BD26">
+        <v>0</v>
+      </c>
+      <c r="BE26">
+        <v>0</v>
+      </c>
+      <c r="BF26">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH26" t="str">
+        <v/>
+      </c>
+      <c r="BI26" t="str">
+        <v/>
+      </c>
+      <c r="BJ26" t="str">
+        <v/>
+      </c>
+      <c r="BK26" t="str">
+        <v/>
+      </c>
+      <c r="BL26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>SHP-026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C27" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27">
+        <v>1553</v>
+      </c>
+      <c r="F27" t="str">
+        <v>2026-06-18T12:00:00.000Z</v>
+      </c>
+      <c r="G27" t="str">
+        <v>2026-06-19T09:00:00.000Z</v>
+      </c>
+      <c r="H27" t="str">
+        <v>2026-06-19T12:00:00.000Z</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L27" t="str">
+        <v>prod-flu</v>
+      </c>
+      <c r="M27" t="str">
+        <v>Influenza Vaccine</v>
+      </c>
+      <c r="N27" t="str">
+        <v>Vaccine</v>
+      </c>
+      <c r="O27" t="str">
+        <v>Cold chain 2–8°C</v>
+      </c>
+      <c r="P27">
+        <v>2</v>
+      </c>
+      <c r="Q27">
+        <v>8</v>
+      </c>
+      <c r="R27" t="str">
+        <v>03000000000048</v>
+      </c>
+      <c r="S27" t="str">
+        <v>BN-2026-003</v>
+      </c>
+      <c r="T27" t="str">
+        <v>2026-05-03T12:00:00.000Z</v>
+      </c>
+      <c r="U27" t="str">
+        <v>2027-06-08T12:00:00.000Z</v>
+      </c>
+      <c r="V27" t="str">
+        <v>BioNTech Marburg GmbH</v>
+      </c>
+      <c r="W27" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="X27">
+        <v>36000</v>
+      </c>
+      <c r="Y27" t="str">
+        <v>car-b</v>
+      </c>
+      <c r="Z27" t="str">
+        <v>Carrier B Freight</v>
+      </c>
+      <c r="AA27" t="str">
+        <v>OCEAN | TRUCK</v>
+      </c>
+      <c r="AB27">
+        <v>50</v>
+      </c>
+      <c r="AC27">
+        <v>64</v>
+      </c>
+      <c r="AD27" t="str">
+        <v>loc-port-rotterdam</v>
+      </c>
+      <c r="AE27" t="str">
+        <v>Port of Rotterdam</v>
+      </c>
+      <c r="AF27" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG27" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="AH27">
+        <v>51.9496</v>
+      </c>
+      <c r="AI27">
+        <v>4.1453</v>
+      </c>
+      <c r="AJ27" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK27" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL27" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM27" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN27">
+        <v>33.749</v>
+      </c>
+      <c r="AO27">
+        <v>-84.388</v>
+      </c>
+      <c r="AP27">
+        <v>6</v>
+      </c>
+      <c r="AQ27">
+        <v>6</v>
+      </c>
+      <c r="AR27">
+        <v>1</v>
+      </c>
+      <c r="AS27">
+        <v>2</v>
+      </c>
+      <c r="AT27" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU27">
+        <v>9</v>
+      </c>
+      <c r="AV27">
+        <v>4.1</v>
+      </c>
+      <c r="AW27">
+        <v>5.9</v>
+      </c>
+      <c r="AX27">
+        <v>4.9</v>
+      </c>
+      <c r="AY27">
+        <v>0</v>
+      </c>
+      <c r="AZ27">
+        <v>1</v>
+      </c>
+      <c r="BA27">
+        <v>1</v>
+      </c>
+      <c r="BB27">
+        <v>0</v>
+      </c>
+      <c r="BC27">
+        <v>0</v>
+      </c>
+      <c r="BD27">
+        <v>0</v>
+      </c>
+      <c r="BE27">
+        <v>1</v>
+      </c>
+      <c r="BF27">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="str">
+        <v>North Atlantic Storm System | Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH27" t="str">
+        <v/>
+      </c>
+      <c r="BI27" t="str">
+        <v/>
+      </c>
+      <c r="BJ27" t="str">
+        <v/>
+      </c>
+      <c r="BK27" t="str">
+        <v/>
+      </c>
+      <c r="BL27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>SHP-027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>DELAYED</v>
+      </c>
+      <c r="C28" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D28">
+        <v>24</v>
+      </c>
+      <c r="E28">
+        <v>1787</v>
+      </c>
+      <c r="F28" t="str">
+        <v>2026-06-22T12:00:00.000Z</v>
+      </c>
+      <c r="G28" t="str">
+        <v>2026-06-30T12:00:00.000Z</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L28" t="str">
+        <v>prod-metformin</v>
+      </c>
+      <c r="M28" t="str">
+        <v>Metformin Tablets</v>
+      </c>
+      <c r="N28" t="str">
+        <v>Antidiabetic</v>
+      </c>
+      <c r="O28" t="str">
+        <v>Ambient 15–30°C</v>
+      </c>
+      <c r="P28">
+        <v>15</v>
+      </c>
+      <c r="Q28">
+        <v>30</v>
+      </c>
+      <c r="R28" t="str">
+        <v>03000000000079</v>
+      </c>
+      <c r="S28" t="str">
+        <v>BN-2026-011</v>
+      </c>
+      <c r="T28" t="str">
+        <v>2026-03-09T12:00:00.000Z</v>
+      </c>
+      <c r="U28" t="str">
+        <v>2026-12-28T12:00:00.000Z</v>
+      </c>
+      <c r="V28" t="str">
+        <v>Generic Pharma Mumbai Ltd</v>
+      </c>
+      <c r="W28" t="str">
+        <v>India</v>
+      </c>
+      <c r="X28">
+        <v>24000</v>
+      </c>
+      <c r="Y28" t="str">
+        <v>car-h</v>
+      </c>
+      <c r="Z28" t="str">
+        <v>Global Air Freight</v>
+      </c>
+      <c r="AA28" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="AB28">
+        <v>75</v>
+      </c>
+      <c r="AC28">
+        <v>63</v>
+      </c>
+      <c r="AD28" t="str">
+        <v>loc-air-fra</v>
+      </c>
+      <c r="AE28" t="str">
+        <v>Frankfurt Air Cargo Hub</v>
+      </c>
+      <c r="AF28" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG28" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH28">
+        <v>50.0379</v>
+      </c>
+      <c r="AI28">
+        <v>8.5622</v>
+      </c>
+      <c r="AJ28" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK28" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL28" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM28" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN28">
+        <v>33.749</v>
+      </c>
+      <c r="AO28">
+        <v>-84.388</v>
+      </c>
+      <c r="AP28">
+        <v>5</v>
+      </c>
+      <c r="AQ28">
+        <v>6</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>2</v>
+      </c>
+      <c r="AT28" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU28">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="str">
+        <v/>
+      </c>
+      <c r="AW28" t="str">
+        <v/>
+      </c>
+      <c r="AX28" t="str">
+        <v/>
+      </c>
+      <c r="AY28">
+        <v>0</v>
+      </c>
+      <c r="AZ28">
+        <v>1</v>
+      </c>
+      <c r="BA28">
+        <v>1</v>
+      </c>
+      <c r="BB28">
+        <v>1</v>
+      </c>
+      <c r="BC28">
+        <v>0</v>
+      </c>
+      <c r="BD28">
+        <v>0</v>
+      </c>
+      <c r="BE28">
+        <v>0</v>
+      </c>
+      <c r="BF28">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH28" t="str">
+        <v/>
+      </c>
+      <c r="BI28" t="str">
+        <v/>
+      </c>
+      <c r="BJ28" t="str">
+        <v/>
+      </c>
+      <c r="BK28" t="str">
+        <v/>
+      </c>
+      <c r="BL28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>SHP-028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>IN_TRANSIT</v>
+      </c>
+      <c r="C29" t="str">
+        <v>TRUCK</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>1531</v>
+      </c>
+      <c r="F29" t="str">
+        <v>2026-06-15T12:00:00.000Z</v>
+      </c>
+      <c r="G29" t="str">
+        <v>2026-07-04T12:00:00.000Z</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L29" t="str">
+        <v>prod-atorva</v>
+      </c>
+      <c r="M29" t="str">
+        <v>Atorvastatin Tablets</v>
+      </c>
+      <c r="N29" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="O29" t="str">
+        <v>Ambient 15–30°C</v>
+      </c>
+      <c r="P29">
+        <v>15</v>
+      </c>
+      <c r="Q29">
+        <v>30</v>
+      </c>
+      <c r="R29" t="str">
+        <v>03000000000062</v>
+      </c>
+      <c r="S29" t="str">
+        <v>BN-2026-002</v>
+      </c>
+      <c r="T29" t="str">
+        <v>2026-02-09T12:00:00.000Z</v>
+      </c>
+      <c r="U29" t="str">
+        <v>2026-11-01T12:00:00.000Z</v>
+      </c>
+      <c r="V29" t="str">
+        <v>Generic Pharma Mumbai Ltd</v>
+      </c>
+      <c r="W29" t="str">
+        <v>India</v>
+      </c>
+      <c r="X29">
+        <v>34000</v>
+      </c>
+      <c r="Y29" t="str">
+        <v>car-b</v>
+      </c>
+      <c r="Z29" t="str">
+        <v>Carrier B Freight</v>
+      </c>
+      <c r="AA29" t="str">
+        <v>OCEAN | TRUCK</v>
+      </c>
+      <c r="AB29">
+        <v>50</v>
+      </c>
+      <c r="AC29">
+        <v>64</v>
+      </c>
+      <c r="AD29" t="str">
+        <v>loc-dc-chicago</v>
+      </c>
+      <c r="AE29" t="str">
+        <v>Midwest Distribution Center — Chicago</v>
+      </c>
+      <c r="AF29" t="str">
+        <v>DC</v>
+      </c>
+      <c r="AG29" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AH29">
+        <v>41.8781</v>
+      </c>
+      <c r="AI29">
+        <v>-87.6298</v>
+      </c>
+      <c r="AJ29" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK29" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL29" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM29" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN29">
+        <v>40.7903</v>
+      </c>
+      <c r="AO29">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP29">
+        <v>3</v>
+      </c>
+      <c r="AQ29">
+        <v>6</v>
+      </c>
+      <c r="AR29">
+        <v>3</v>
+      </c>
+      <c r="AS29">
+        <v>2</v>
+      </c>
+      <c r="AT29" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU29">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="str">
+        <v/>
+      </c>
+      <c r="AW29" t="str">
+        <v/>
+      </c>
+      <c r="AX29" t="str">
+        <v/>
+      </c>
+      <c r="AY29">
+        <v>0</v>
+      </c>
+      <c r="AZ29">
+        <v>1</v>
+      </c>
+      <c r="BA29">
+        <v>1</v>
+      </c>
+      <c r="BB29">
+        <v>0</v>
+      </c>
+      <c r="BC29">
+        <v>0</v>
+      </c>
+      <c r="BD29">
+        <v>0</v>
+      </c>
+      <c r="BE29">
+        <v>1</v>
+      </c>
+      <c r="BF29">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH29" t="str">
+        <v/>
+      </c>
+      <c r="BI29" t="str">
+        <v/>
+      </c>
+      <c r="BJ29" t="str">
+        <v/>
+      </c>
+      <c r="BK29" t="str">
+        <v/>
+      </c>
+      <c r="BL29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>SHP-029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>DELAYED</v>
+      </c>
+      <c r="C30" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D30">
+        <v>42</v>
+      </c>
+      <c r="E30">
+        <v>1016</v>
+      </c>
+      <c r="F30" t="str">
+        <v>2026-06-17T12:00:00.000Z</v>
+      </c>
+      <c r="G30" t="str">
+        <v>2026-07-05T12:00:00.000Z</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L30" t="str">
+        <v>prod-salbutamol</v>
+      </c>
+      <c r="M30" t="str">
+        <v>Salbutamol Inhaler</v>
+      </c>
+      <c r="N30" t="str">
+        <v>Respiratory</v>
+      </c>
+      <c r="O30" t="str">
+        <v>Controlled room 15–25°C</v>
+      </c>
+      <c r="P30">
+        <v>15</v>
+      </c>
+      <c r="Q30">
+        <v>25</v>
+      </c>
+      <c r="R30" t="str">
+        <v>03000000000109</v>
+      </c>
+      <c r="S30" t="str">
+        <v>BN-2026-019</v>
+      </c>
+      <c r="T30" t="str">
+        <v>2026-04-27T12:00:00.000Z</v>
+      </c>
+      <c r="U30" t="str">
+        <v>2027-12-08T12:00:00.000Z</v>
+      </c>
+      <c r="V30" t="str">
+        <v>Pacific Biologics Co</v>
+      </c>
+      <c r="W30" t="str">
+        <v>China</v>
+      </c>
+      <c r="X30">
+        <v>30000</v>
+      </c>
+      <c r="Y30" t="str">
+        <v>car-c</v>
+      </c>
+      <c r="Z30" t="str">
+        <v>SkyCargo Air</v>
+      </c>
+      <c r="AA30" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="AB30">
+        <v>33</v>
+      </c>
+      <c r="AC30">
+        <v>48</v>
+      </c>
+      <c r="AD30" t="str">
+        <v>loc-air-fra</v>
+      </c>
+      <c r="AE30" t="str">
+        <v>Frankfurt Air Cargo Hub</v>
+      </c>
+      <c r="AF30" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG30" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH30">
+        <v>50.0379</v>
+      </c>
+      <c r="AI30">
+        <v>8.5622</v>
+      </c>
+      <c r="AJ30" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK30" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL30" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM30" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN30">
+        <v>33.749</v>
+      </c>
+      <c r="AO30">
+        <v>-84.388</v>
+      </c>
+      <c r="AP30">
+        <v>5</v>
+      </c>
+      <c r="AQ30">
+        <v>6</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>2</v>
+      </c>
+      <c r="AT30" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU30">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="str">
+        <v/>
+      </c>
+      <c r="AW30" t="str">
+        <v/>
+      </c>
+      <c r="AX30" t="str">
+        <v/>
+      </c>
+      <c r="AY30">
+        <v>0</v>
+      </c>
+      <c r="AZ30">
+        <v>1</v>
+      </c>
+      <c r="BA30">
+        <v>1</v>
+      </c>
+      <c r="BB30">
+        <v>1</v>
+      </c>
+      <c r="BC30">
+        <v>0</v>
+      </c>
+      <c r="BD30">
+        <v>0</v>
+      </c>
+      <c r="BE30">
+        <v>0</v>
+      </c>
+      <c r="BF30">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH30" t="str">
+        <v/>
+      </c>
+      <c r="BI30" t="str">
+        <v/>
+      </c>
+      <c r="BJ30" t="str">
+        <v/>
+      </c>
+      <c r="BK30" t="str">
+        <v/>
+      </c>
+      <c r="BL30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>SHP-030</v>
+      </c>
+      <c r="B31" t="str">
+        <v>IN_TRANSIT</v>
+      </c>
+      <c r="C31" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>1251</v>
+      </c>
+      <c r="F31" t="str">
+        <v>2026-05-30T12:00:00.000Z</v>
+      </c>
+      <c r="G31" t="str">
+        <v>2026-06-28T12:00:00.000Z</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L31" t="str">
+        <v>prod-salbutamol</v>
+      </c>
+      <c r="M31" t="str">
+        <v>Salbutamol Inhaler</v>
+      </c>
+      <c r="N31" t="str">
+        <v>Respiratory</v>
+      </c>
+      <c r="O31" t="str">
+        <v>Controlled room 15–25°C</v>
+      </c>
+      <c r="P31">
+        <v>15</v>
+      </c>
+      <c r="Q31">
+        <v>25</v>
+      </c>
+      <c r="R31" t="str">
+        <v>03000000000109</v>
+      </c>
+      <c r="S31" t="str">
+        <v>BN-2026-005</v>
+      </c>
+      <c r="T31" t="str">
+        <v>2026-02-01T12:00:00.000Z</v>
+      </c>
+      <c r="U31" t="str">
+        <v>2027-03-21T12:00:00.000Z</v>
+      </c>
+      <c r="V31" t="str">
+        <v>BioNTech Marburg GmbH</v>
+      </c>
+      <c r="W31" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="X31">
+        <v>5000</v>
+      </c>
+      <c r="Y31" t="str">
+        <v>car-a</v>
+      </c>
+      <c r="Z31" t="str">
+        <v>Atlantic Ocean Lines</v>
+      </c>
+      <c r="AA31" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="AB31">
+        <v>100</v>
+      </c>
+      <c r="AC31">
+        <v>66</v>
+      </c>
+      <c r="AD31" t="str">
+        <v>loc-port-hamburg</v>
+      </c>
+      <c r="AE31" t="str">
+        <v>Port of Hamburg</v>
+      </c>
+      <c r="AF31" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG31" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH31">
+        <v>53.5413</v>
+      </c>
+      <c r="AI31">
+        <v>9.9326</v>
+      </c>
+      <c r="AJ31" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK31" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL31" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM31" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN31">
+        <v>33.749</v>
+      </c>
+      <c r="AO31">
+        <v>-84.388</v>
+      </c>
+      <c r="AP31">
+        <v>6</v>
+      </c>
+      <c r="AQ31">
+        <v>6</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>2</v>
+      </c>
+      <c r="AT31" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU31">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="str">
+        <v/>
+      </c>
+      <c r="AW31" t="str">
+        <v/>
+      </c>
+      <c r="AX31" t="str">
+        <v/>
+      </c>
+      <c r="AY31">
+        <v>0</v>
+      </c>
+      <c r="AZ31">
+        <v>0</v>
+      </c>
+      <c r="BA31">
+        <v>0</v>
+      </c>
+      <c r="BB31">
+        <v>0</v>
+      </c>
+      <c r="BC31">
+        <v>0</v>
+      </c>
+      <c r="BD31">
+        <v>0</v>
+      </c>
+      <c r="BE31">
+        <v>0</v>
+      </c>
+      <c r="BF31">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="str">
+        <v>North Atlantic Storm System | Customs Congestion — Newark | Heatwave — US Northeast | Fog — Port of Hamburg</v>
+      </c>
+      <c r="BH31" t="str">
+        <v>RCL-2025-014</v>
+      </c>
+      <c r="BI31" t="str">
+        <v>CLOSED</v>
+      </c>
+      <c r="BJ31">
+        <v>5200</v>
+      </c>
+      <c r="BK31">
+        <v>5200</v>
+      </c>
+      <c r="BL31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>SHP-031</v>
+      </c>
+      <c r="B32" t="str">
+        <v>IN_TRANSIT</v>
+      </c>
+      <c r="C32" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>1556</v>
+      </c>
+      <c r="F32" t="str">
+        <v>2026-06-16T12:00:00.000Z</v>
+      </c>
+      <c r="G32" t="str">
+        <v>2026-06-26T12:00:00.000Z</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L32" t="str">
+        <v>prod-flu</v>
+      </c>
+      <c r="M32" t="str">
+        <v>Influenza Vaccine</v>
+      </c>
+      <c r="N32" t="str">
+        <v>Vaccine</v>
+      </c>
+      <c r="O32" t="str">
+        <v>Cold chain 2–8°C</v>
+      </c>
+      <c r="P32">
+        <v>2</v>
+      </c>
+      <c r="Q32">
+        <v>8</v>
+      </c>
+      <c r="R32" t="str">
+        <v>03000000000048</v>
+      </c>
+      <c r="S32" t="str">
+        <v>BN-2026-008</v>
+      </c>
+      <c r="T32" t="str">
+        <v>2026-05-08T12:00:00.000Z</v>
+      </c>
+      <c r="U32" t="str">
+        <v>2027-08-04T12:00:00.000Z</v>
+      </c>
+      <c r="V32" t="str">
+        <v>BioNTech Marburg GmbH</v>
+      </c>
+      <c r="W32" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="X32">
+        <v>8000</v>
+      </c>
+      <c r="Y32" t="str">
+        <v>car-g</v>
+      </c>
+      <c r="Z32" t="str">
+        <v>ABC Logistics</v>
+      </c>
+      <c r="AA32" t="str">
+        <v>TRUCK | AIR</v>
+      </c>
+      <c r="AB32">
+        <v>100</v>
+      </c>
+      <c r="AC32">
+        <v>81</v>
+      </c>
+      <c r="AD32" t="str">
+        <v>loc-air-lhr</v>
+      </c>
+      <c r="AE32" t="str">
+        <v>Heathrow Air Cargo Hub</v>
+      </c>
+      <c r="AF32" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG32" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="AH32">
+        <v>51.47</v>
+      </c>
+      <c r="AI32">
+        <v>-0.4543</v>
+      </c>
+      <c r="AJ32" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK32" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL32" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM32" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN32">
+        <v>33.749</v>
+      </c>
+      <c r="AO32">
+        <v>-84.388</v>
+      </c>
+      <c r="AP32">
+        <v>5</v>
+      </c>
+      <c r="AQ32">
+        <v>6</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>2</v>
+      </c>
+      <c r="AT32" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU32">
+        <v>73</v>
+      </c>
+      <c r="AV32">
+        <v>3.7</v>
+      </c>
+      <c r="AW32">
+        <v>6.5</v>
+      </c>
+      <c r="AX32">
+        <v>5.1</v>
+      </c>
+      <c r="AY32">
+        <v>0</v>
+      </c>
+      <c r="AZ32">
+        <v>0</v>
+      </c>
+      <c r="BA32">
+        <v>0</v>
+      </c>
+      <c r="BB32">
+        <v>0</v>
+      </c>
+      <c r="BC32">
+        <v>0</v>
+      </c>
+      <c r="BD32">
+        <v>0</v>
+      </c>
+      <c r="BE32">
+        <v>0</v>
+      </c>
+      <c r="BF32">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH32" t="str">
+        <v/>
+      </c>
+      <c r="BI32" t="str">
+        <v/>
+      </c>
+      <c r="BJ32" t="str">
+        <v/>
+      </c>
+      <c r="BK32" t="str">
+        <v/>
+      </c>
+      <c r="BL32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>SHP-032</v>
+      </c>
+      <c r="B33" t="str">
+        <v>DELAYED</v>
+      </c>
+      <c r="C33" t="str">
+        <v>TRUCK</v>
+      </c>
+      <c r="D33">
+        <v>29</v>
+      </c>
+      <c r="E33">
+        <v>1401</v>
+      </c>
+      <c r="F33" t="str">
+        <v>2026-06-18T12:00:00.000Z</v>
+      </c>
+      <c r="G33" t="str">
+        <v>2026-07-04T12:00:00.000Z</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L33" t="str">
+        <v>prod-amox</v>
+      </c>
+      <c r="M33" t="str">
+        <v>Amoxicillin Capsules</v>
+      </c>
+      <c r="N33" t="str">
+        <v>Antibiotic</v>
+      </c>
+      <c r="O33" t="str">
+        <v>Ambient 15–25°C</v>
+      </c>
+      <c r="P33">
+        <v>15</v>
+      </c>
+      <c r="Q33">
+        <v>25</v>
+      </c>
+      <c r="R33" t="str">
+        <v>03000000000055</v>
+      </c>
+      <c r="S33" t="str">
+        <v>BN-2026-014</v>
+      </c>
+      <c r="T33" t="str">
+        <v>2026-03-05T12:00:00.000Z</v>
+      </c>
+      <c r="U33" t="str">
+        <v>2028-01-09T12:00:00.000Z</v>
+      </c>
+      <c r="V33" t="str">
+        <v>Pacific Biologics Co</v>
+      </c>
+      <c r="W33" t="str">
+        <v>China</v>
+      </c>
+      <c r="X33">
+        <v>19000</v>
+      </c>
+      <c r="Y33" t="str">
+        <v>car-b</v>
+      </c>
+      <c r="Z33" t="str">
+        <v>Carrier B Freight</v>
+      </c>
+      <c r="AA33" t="str">
+        <v>OCEAN | TRUCK</v>
+      </c>
+      <c r="AB33">
+        <v>50</v>
+      </c>
+      <c r="AC33">
+        <v>64</v>
+      </c>
+      <c r="AD33" t="str">
+        <v>loc-3pl-dallas</v>
+      </c>
+      <c r="AE33" t="str">
+        <v>3PL Warehouse — Dallas TX</v>
+      </c>
+      <c r="AF33" t="str">
+        <v>3PL</v>
+      </c>
+      <c r="AG33" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AH33">
+        <v>32.7767</v>
+      </c>
+      <c r="AI33">
+        <v>-96.797</v>
+      </c>
+      <c r="AJ33" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK33" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL33" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM33" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN33">
+        <v>33.749</v>
+      </c>
+      <c r="AO33">
+        <v>-84.388</v>
+      </c>
+      <c r="AP33">
+        <v>3</v>
+      </c>
+      <c r="AQ33">
+        <v>6</v>
+      </c>
+      <c r="AR33">
+        <v>1</v>
+      </c>
+      <c r="AS33">
+        <v>2</v>
+      </c>
+      <c r="AT33" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU33">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="str">
+        <v/>
+      </c>
+      <c r="AW33" t="str">
+        <v/>
+      </c>
+      <c r="AX33" t="str">
+        <v/>
+      </c>
+      <c r="AY33">
+        <v>0</v>
+      </c>
+      <c r="AZ33">
+        <v>2</v>
+      </c>
+      <c r="BA33">
+        <v>2</v>
+      </c>
+      <c r="BB33">
+        <v>1</v>
+      </c>
+      <c r="BC33">
+        <v>0</v>
+      </c>
+      <c r="BD33">
+        <v>0</v>
+      </c>
+      <c r="BE33">
+        <v>1</v>
+      </c>
+      <c r="BF33">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="str">
+        <v/>
+      </c>
+      <c r="BH33" t="str">
+        <v/>
+      </c>
+      <c r="BI33" t="str">
+        <v/>
+      </c>
+      <c r="BJ33" t="str">
+        <v/>
+      </c>
+      <c r="BK33" t="str">
+        <v/>
+      </c>
+      <c r="BL33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>SHP-033</v>
+      </c>
+      <c r="B34" t="str">
+        <v>DELAYED</v>
+      </c>
+      <c r="C34" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D34">
+        <v>26</v>
+      </c>
+      <c r="E34">
+        <v>1184</v>
+      </c>
+      <c r="F34" t="str">
+        <v>2026-06-19T12:00:00.000Z</v>
+      </c>
+      <c r="G34" t="str">
+        <v>2026-07-04T12:00:00.000Z</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L34" t="str">
+        <v>prod-metformin</v>
+      </c>
+      <c r="M34" t="str">
+        <v>Metformin Tablets</v>
+      </c>
+      <c r="N34" t="str">
+        <v>Antidiabetic</v>
+      </c>
+      <c r="O34" t="str">
+        <v>Ambient 15–30°C</v>
+      </c>
+      <c r="P34">
+        <v>15</v>
+      </c>
+      <c r="Q34">
+        <v>30</v>
+      </c>
+      <c r="R34" t="str">
+        <v>03000000000079</v>
+      </c>
+      <c r="S34" t="str">
+        <v>BN-2026-011</v>
+      </c>
+      <c r="T34" t="str">
+        <v>2026-03-09T12:00:00.000Z</v>
+      </c>
+      <c r="U34" t="str">
+        <v>2026-12-28T12:00:00.000Z</v>
+      </c>
+      <c r="V34" t="str">
+        <v>Generic Pharma Mumbai Ltd</v>
+      </c>
+      <c r="W34" t="str">
+        <v>India</v>
+      </c>
+      <c r="X34">
+        <v>24000</v>
+      </c>
+      <c r="Y34" t="str">
+        <v>car-h</v>
+      </c>
+      <c r="Z34" t="str">
+        <v>Global Air Freight</v>
+      </c>
+      <c r="AA34" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="AB34">
+        <v>75</v>
+      </c>
+      <c r="AC34">
+        <v>63</v>
+      </c>
+      <c r="AD34" t="str">
+        <v>loc-air-fra</v>
+      </c>
+      <c r="AE34" t="str">
+        <v>Frankfurt Air Cargo Hub</v>
+      </c>
+      <c r="AF34" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG34" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH34">
+        <v>50.0379</v>
+      </c>
+      <c r="AI34">
+        <v>8.5622</v>
+      </c>
+      <c r="AJ34" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK34" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL34" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM34" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN34">
+        <v>40.7903</v>
+      </c>
+      <c r="AO34">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP34">
+        <v>5</v>
+      </c>
+      <c r="AQ34">
+        <v>6</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>2</v>
+      </c>
+      <c r="AT34" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU34">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="str">
+        <v/>
+      </c>
+      <c r="AW34" t="str">
+        <v/>
+      </c>
+      <c r="AX34" t="str">
+        <v/>
+      </c>
+      <c r="AY34">
+        <v>0</v>
+      </c>
+      <c r="AZ34">
+        <v>1</v>
+      </c>
+      <c r="BA34">
+        <v>1</v>
+      </c>
+      <c r="BB34">
+        <v>1</v>
+      </c>
+      <c r="BC34">
+        <v>0</v>
+      </c>
+      <c r="BD34">
+        <v>0</v>
+      </c>
+      <c r="BE34">
+        <v>0</v>
+      </c>
+      <c r="BF34">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH34" t="str">
+        <v/>
+      </c>
+      <c r="BI34" t="str">
+        <v/>
+      </c>
+      <c r="BJ34" t="str">
+        <v/>
+      </c>
+      <c r="BK34" t="str">
+        <v/>
+      </c>
+      <c r="BL34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>SHP-034</v>
+      </c>
+      <c r="B35" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C35" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>1918</v>
+      </c>
+      <c r="F35" t="str">
+        <v>2026-06-23T12:00:00.000Z</v>
+      </c>
+      <c r="G35" t="str">
+        <v>2026-06-14T12:00:00.000Z</v>
+      </c>
+      <c r="H35" t="str">
+        <v>2026-06-14T12:00:00.000Z</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L35" t="str">
+        <v>prod-amox</v>
+      </c>
+      <c r="M35" t="str">
+        <v>Amoxicillin Capsules</v>
+      </c>
+      <c r="N35" t="str">
+        <v>Antibiotic</v>
+      </c>
+      <c r="O35" t="str">
+        <v>Ambient 15–25°C</v>
+      </c>
+      <c r="P35">
+        <v>15</v>
+      </c>
+      <c r="Q35">
+        <v>25</v>
+      </c>
+      <c r="R35" t="str">
+        <v>03000000000055</v>
+      </c>
+      <c r="S35" t="str">
+        <v>BN-2026-014</v>
+      </c>
+      <c r="T35" t="str">
+        <v>2026-03-05T12:00:00.000Z</v>
+      </c>
+      <c r="U35" t="str">
+        <v>2028-01-09T12:00:00.000Z</v>
+      </c>
+      <c r="V35" t="str">
+        <v>Pacific Biologics Co</v>
+      </c>
+      <c r="W35" t="str">
+        <v>China</v>
+      </c>
+      <c r="X35">
+        <v>19000</v>
+      </c>
+      <c r="Y35" t="str">
+        <v>car-e</v>
+      </c>
+      <c r="Z35" t="str">
+        <v>Pacific Maritime</v>
+      </c>
+      <c r="AA35" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="AB35">
+        <v>75</v>
+      </c>
+      <c r="AC35">
+        <v>80</v>
+      </c>
+      <c r="AD35" t="str">
+        <v>loc-port-hamburg</v>
+      </c>
+      <c r="AE35" t="str">
+        <v>Port of Hamburg</v>
+      </c>
+      <c r="AF35" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG35" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH35">
+        <v>53.5413</v>
+      </c>
+      <c r="AI35">
+        <v>9.9326</v>
+      </c>
+      <c r="AJ35" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK35" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL35" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM35" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN35">
+        <v>40.7903</v>
+      </c>
+      <c r="AO35">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP35">
+        <v>6</v>
+      </c>
+      <c r="AQ35">
+        <v>6</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>2</v>
+      </c>
+      <c r="AT35" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU35">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="str">
+        <v/>
+      </c>
+      <c r="AW35" t="str">
+        <v/>
+      </c>
+      <c r="AX35" t="str">
+        <v/>
+      </c>
+      <c r="AY35">
+        <v>0</v>
+      </c>
+      <c r="AZ35">
+        <v>0</v>
+      </c>
+      <c r="BA35">
+        <v>0</v>
+      </c>
+      <c r="BB35">
+        <v>0</v>
+      </c>
+      <c r="BC35">
+        <v>0</v>
+      </c>
+      <c r="BD35">
+        <v>0</v>
+      </c>
+      <c r="BE35">
+        <v>0</v>
+      </c>
+      <c r="BF35">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="str">
+        <v>North Atlantic Storm System | Customs Congestion — Newark | Heatwave — US Northeast | Fog — Port of Hamburg</v>
+      </c>
+      <c r="BH35" t="str">
+        <v/>
+      </c>
+      <c r="BI35" t="str">
+        <v/>
+      </c>
+      <c r="BJ35" t="str">
+        <v/>
+      </c>
+      <c r="BK35" t="str">
+        <v/>
+      </c>
+      <c r="BL35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>SHP-035</v>
+      </c>
+      <c r="B36" t="str">
+        <v>DELAYED</v>
+      </c>
+      <c r="C36" t="str">
+        <v>RAIL</v>
+      </c>
+      <c r="D36">
+        <v>27</v>
+      </c>
+      <c r="E36">
+        <v>1829</v>
+      </c>
+      <c r="F36" t="str">
+        <v>2026-06-16T12:00:00.000Z</v>
+      </c>
+      <c r="G36" t="str">
+        <v>2026-07-04T12:00:00.000Z</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L36" t="str">
+        <v>prod-insulin</v>
+      </c>
+      <c r="M36" t="str">
+        <v>Insulin Glargine Injection</v>
+      </c>
+      <c r="N36" t="str">
+        <v>Biologic (Antidiabetic)</v>
+      </c>
+      <c r="O36" t="str">
+        <v>Cold chain 2–8°C</v>
+      </c>
+      <c r="P36">
+        <v>2</v>
+      </c>
+      <c r="Q36">
+        <v>8</v>
+      </c>
+      <c r="R36" t="str">
+        <v>03000000000024</v>
+      </c>
+      <c r="S36" t="str">
+        <v>BN-2026-012</v>
+      </c>
+      <c r="T36" t="str">
+        <v>2026-05-19T12:00:00.000Z</v>
+      </c>
+      <c r="U36" t="str">
+        <v>2027-04-15T12:00:00.000Z</v>
+      </c>
+      <c r="V36" t="str">
+        <v>BioNTech Marburg GmbH</v>
+      </c>
+      <c r="W36" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="X36">
+        <v>4000</v>
+      </c>
+      <c r="Y36" t="str">
+        <v>car-f</v>
+      </c>
+      <c r="Z36" t="str">
+        <v>EuroRail Logistics</v>
+      </c>
+      <c r="AA36" t="str">
+        <v>RAIL | TRUCK</v>
+      </c>
+      <c r="AB36">
+        <v>100</v>
+      </c>
+      <c r="AC36">
+        <v>62</v>
+      </c>
+      <c r="AD36" t="str">
+        <v>loc-port-newark</v>
+      </c>
+      <c r="AE36" t="str">
+        <v>Port of Newark</v>
+      </c>
+      <c r="AF36" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG36" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AH36">
+        <v>40.6895</v>
+      </c>
+      <c r="AI36">
+        <v>-74.1745</v>
+      </c>
+      <c r="AJ36" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK36" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL36" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM36" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN36">
+        <v>40.7903</v>
+      </c>
+      <c r="AO36">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP36">
+        <v>3</v>
+      </c>
+      <c r="AQ36">
+        <v>6</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>2</v>
+      </c>
+      <c r="AT36" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU36">
+        <v>73</v>
+      </c>
+      <c r="AV36">
+        <v>2.9</v>
+      </c>
+      <c r="AW36">
+        <v>6.7</v>
+      </c>
+      <c r="AX36">
+        <v>4.9</v>
+      </c>
+      <c r="AY36">
+        <v>0</v>
+      </c>
+      <c r="AZ36">
+        <v>1</v>
+      </c>
+      <c r="BA36">
+        <v>1</v>
+      </c>
+      <c r="BB36">
+        <v>1</v>
+      </c>
+      <c r="BC36">
+        <v>0</v>
+      </c>
+      <c r="BD36">
+        <v>0</v>
+      </c>
+      <c r="BE36">
+        <v>0</v>
+      </c>
+      <c r="BF36">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH36" t="str">
+        <v/>
+      </c>
+      <c r="BI36" t="str">
+        <v/>
+      </c>
+      <c r="BJ36" t="str">
+        <v/>
+      </c>
+      <c r="BK36" t="str">
+        <v/>
+      </c>
+      <c r="BL36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>SHP-036</v>
+      </c>
+      <c r="B37" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C37" t="str">
+        <v>TRUCK</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>1036</v>
+      </c>
+      <c r="F37" t="str">
+        <v>2026-06-23T12:00:00.000Z</v>
+      </c>
+      <c r="G37" t="str">
+        <v>2026-06-17T12:00:00.000Z</v>
+      </c>
+      <c r="H37" t="str">
+        <v>2026-06-17T12:00:00.000Z</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L37" t="str">
+        <v>prod-omeprazole</v>
+      </c>
+      <c r="M37" t="str">
+        <v>Omeprazole Capsules</v>
+      </c>
+      <c r="N37" t="str">
+        <v>Gastrointestinal</v>
+      </c>
+      <c r="O37" t="str">
+        <v>Ambient 15–25°C</v>
+      </c>
+      <c r="P37">
+        <v>15</v>
+      </c>
+      <c r="Q37">
+        <v>25</v>
+      </c>
+      <c r="R37" t="str">
+        <v>03000000000093</v>
+      </c>
+      <c r="S37" t="str">
+        <v>BN-2026-016</v>
+      </c>
+      <c r="T37" t="str">
+        <v>2026-04-04T12:00:00.000Z</v>
+      </c>
+      <c r="U37" t="str">
+        <v>2026-12-31T12:00:00.000Z</v>
+      </c>
+      <c r="V37" t="str">
+        <v>Generic Pharma Mumbai Ltd</v>
+      </c>
+      <c r="W37" t="str">
+        <v>India</v>
+      </c>
+      <c r="X37">
+        <v>5000</v>
+      </c>
+      <c r="Y37" t="str">
+        <v>car-g</v>
+      </c>
+      <c r="Z37" t="str">
+        <v>ABC Logistics</v>
+      </c>
+      <c r="AA37" t="str">
+        <v>TRUCK | AIR</v>
+      </c>
+      <c r="AB37">
+        <v>100</v>
+      </c>
+      <c r="AC37">
+        <v>81</v>
+      </c>
+      <c r="AD37" t="str">
+        <v>loc-3pl-nj</v>
+      </c>
+      <c r="AE37" t="str">
+        <v>3PL Warehouse — Edison NJ</v>
+      </c>
+      <c r="AF37" t="str">
+        <v>3PL</v>
+      </c>
+      <c r="AG37" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AH37">
+        <v>40.5187</v>
+      </c>
+      <c r="AI37">
+        <v>-74.4121</v>
+      </c>
+      <c r="AJ37" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK37" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL37" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM37" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN37">
+        <v>40.7903</v>
+      </c>
+      <c r="AO37">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP37">
+        <v>3</v>
+      </c>
+      <c r="AQ37">
+        <v>6</v>
+      </c>
+      <c r="AR37">
+        <v>0</v>
+      </c>
+      <c r="AS37">
+        <v>2</v>
+      </c>
+      <c r="AT37" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU37">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="str">
+        <v/>
+      </c>
+      <c r="AW37" t="str">
+        <v/>
+      </c>
+      <c r="AX37" t="str">
+        <v/>
+      </c>
+      <c r="AY37">
+        <v>0</v>
+      </c>
+      <c r="AZ37">
+        <v>0</v>
+      </c>
+      <c r="BA37">
+        <v>0</v>
+      </c>
+      <c r="BB37">
+        <v>0</v>
+      </c>
+      <c r="BC37">
+        <v>0</v>
+      </c>
+      <c r="BD37">
+        <v>0</v>
+      </c>
+      <c r="BE37">
+        <v>0</v>
+      </c>
+      <c r="BF37">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH37" t="str">
+        <v/>
+      </c>
+      <c r="BI37" t="str">
+        <v/>
+      </c>
+      <c r="BJ37" t="str">
+        <v/>
+      </c>
+      <c r="BK37" t="str">
+        <v/>
+      </c>
+      <c r="BL37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>SHP-037</v>
+      </c>
+      <c r="B38" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C38" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>1470</v>
+      </c>
+      <c r="F38" t="str">
+        <v>2026-06-18T12:00:00.000Z</v>
+      </c>
+      <c r="G38" t="str">
+        <v>2026-06-23T12:00:00.000Z</v>
+      </c>
+      <c r="H38" t="str">
+        <v>2026-06-23T12:00:00.000Z</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L38" t="str">
+        <v>prod-flu</v>
+      </c>
+      <c r="M38" t="str">
+        <v>Influenza Vaccine</v>
+      </c>
+      <c r="N38" t="str">
+        <v>Vaccine</v>
+      </c>
+      <c r="O38" t="str">
+        <v>Cold chain 2–8°C</v>
+      </c>
+      <c r="P38">
+        <v>2</v>
+      </c>
+      <c r="Q38">
+        <v>8</v>
+      </c>
+      <c r="R38" t="str">
+        <v>03000000000048</v>
+      </c>
+      <c r="S38" t="str">
+        <v>BN-2026-003</v>
+      </c>
+      <c r="T38" t="str">
+        <v>2026-05-03T12:00:00.000Z</v>
+      </c>
+      <c r="U38" t="str">
+        <v>2027-06-08T12:00:00.000Z</v>
+      </c>
+      <c r="V38" t="str">
+        <v>BioNTech Marburg GmbH</v>
+      </c>
+      <c r="W38" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="X38">
+        <v>36000</v>
+      </c>
+      <c r="Y38" t="str">
+        <v>car-h</v>
+      </c>
+      <c r="Z38" t="str">
+        <v>Global Air Freight</v>
+      </c>
+      <c r="AA38" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="AB38">
+        <v>75</v>
+      </c>
+      <c r="AC38">
+        <v>63</v>
+      </c>
+      <c r="AD38" t="str">
+        <v>loc-air-lhr</v>
+      </c>
+      <c r="AE38" t="str">
+        <v>Heathrow Air Cargo Hub</v>
+      </c>
+      <c r="AF38" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG38" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="AH38">
+        <v>51.47</v>
+      </c>
+      <c r="AI38">
+        <v>-0.4543</v>
+      </c>
+      <c r="AJ38" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK38" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL38" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM38" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN38">
+        <v>33.749</v>
+      </c>
+      <c r="AO38">
+        <v>-84.388</v>
+      </c>
+      <c r="AP38">
+        <v>5</v>
+      </c>
+      <c r="AQ38">
+        <v>6</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>2</v>
+      </c>
+      <c r="AT38" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU38">
+        <v>41</v>
+      </c>
+      <c r="AV38">
+        <v>2.7</v>
+      </c>
+      <c r="AW38">
+        <v>6.1</v>
+      </c>
+      <c r="AX38">
+        <v>4.7</v>
+      </c>
+      <c r="AY38">
+        <v>0</v>
+      </c>
+      <c r="AZ38">
+        <v>0</v>
+      </c>
+      <c r="BA38">
+        <v>0</v>
+      </c>
+      <c r="BB38">
+        <v>0</v>
+      </c>
+      <c r="BC38">
+        <v>0</v>
+      </c>
+      <c r="BD38">
+        <v>0</v>
+      </c>
+      <c r="BE38">
+        <v>0</v>
+      </c>
+      <c r="BF38">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH38" t="str">
+        <v/>
+      </c>
+      <c r="BI38" t="str">
+        <v/>
+      </c>
+      <c r="BJ38" t="str">
+        <v/>
+      </c>
+      <c r="BK38" t="str">
+        <v/>
+      </c>
+      <c r="BL38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>SHP-038</v>
+      </c>
+      <c r="B39" t="str">
+        <v>DELAYED</v>
+      </c>
+      <c r="C39" t="str">
+        <v>OCEAN</v>
+      </c>
+      <c r="D39">
+        <v>51</v>
+      </c>
+      <c r="E39">
+        <v>568</v>
+      </c>
+      <c r="F39" t="str">
+        <v>2026-06-01T12:00:00.000Z</v>
+      </c>
+      <c r="G39" t="str">
+        <v>2026-06-30T12:00:00.000Z</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L39" t="str">
+        <v>prod-insulin</v>
+      </c>
+      <c r="M39" t="str">
+        <v>Insulin Glargine Injection</v>
+      </c>
+      <c r="N39" t="str">
+        <v>Biologic (Antidiabetic)</v>
+      </c>
+      <c r="O39" t="str">
+        <v>Cold chain 2–8°C</v>
+      </c>
+      <c r="P39">
+        <v>2</v>
+      </c>
+      <c r="Q39">
+        <v>8</v>
+      </c>
+      <c r="R39" t="str">
+        <v>03000000000024</v>
+      </c>
+      <c r="S39" t="str">
+        <v>BN-2026-012</v>
+      </c>
+      <c r="T39" t="str">
+        <v>2026-05-19T12:00:00.000Z</v>
+      </c>
+      <c r="U39" t="str">
+        <v>2027-04-15T12:00:00.000Z</v>
+      </c>
+      <c r="V39" t="str">
+        <v>BioNTech Marburg GmbH</v>
+      </c>
+      <c r="W39" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="X39">
+        <v>4000</v>
+      </c>
+      <c r="Y39" t="str">
+        <v>car-b</v>
+      </c>
+      <c r="Z39" t="str">
+        <v>Carrier B Freight</v>
+      </c>
+      <c r="AA39" t="str">
+        <v>OCEAN | TRUCK</v>
+      </c>
+      <c r="AB39">
+        <v>50</v>
+      </c>
+      <c r="AC39">
+        <v>64</v>
+      </c>
+      <c r="AD39" t="str">
+        <v>loc-port-rotterdam</v>
+      </c>
+      <c r="AE39" t="str">
+        <v>Port of Rotterdam</v>
+      </c>
+      <c r="AF39" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG39" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="AH39">
+        <v>51.9496</v>
+      </c>
+      <c r="AI39">
+        <v>4.1453</v>
+      </c>
+      <c r="AJ39" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK39" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL39" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM39" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN39">
+        <v>33.749</v>
+      </c>
+      <c r="AO39">
+        <v>-84.388</v>
+      </c>
+      <c r="AP39">
+        <v>6</v>
+      </c>
+      <c r="AQ39">
+        <v>6</v>
+      </c>
+      <c r="AR39">
+        <v>0</v>
+      </c>
+      <c r="AS39">
+        <v>2</v>
+      </c>
+      <c r="AT39" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU39">
+        <v>193</v>
+      </c>
+      <c r="AV39">
+        <v>3.1</v>
+      </c>
+      <c r="AW39">
+        <v>7</v>
+      </c>
+      <c r="AX39">
+        <v>5</v>
+      </c>
+      <c r="AY39">
+        <v>0</v>
+      </c>
+      <c r="AZ39">
+        <v>1</v>
+      </c>
+      <c r="BA39">
+        <v>1</v>
+      </c>
+      <c r="BB39">
+        <v>1</v>
+      </c>
+      <c r="BC39">
+        <v>0</v>
+      </c>
+      <c r="BD39">
+        <v>0</v>
+      </c>
+      <c r="BE39">
+        <v>0</v>
+      </c>
+      <c r="BF39">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="str">
+        <v>North Atlantic Storm System | Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH39" t="str">
+        <v/>
+      </c>
+      <c r="BI39" t="str">
+        <v/>
+      </c>
+      <c r="BJ39" t="str">
+        <v/>
+      </c>
+      <c r="BK39" t="str">
+        <v/>
+      </c>
+      <c r="BL39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>SHP-039</v>
+      </c>
+      <c r="B40" t="str">
+        <v>IN_TRANSIT</v>
+      </c>
+      <c r="C40" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>2385</v>
+      </c>
+      <c r="F40" t="str">
+        <v>2026-06-20T12:00:00.000Z</v>
+      </c>
+      <c r="G40" t="str">
+        <v>2026-07-01T12:00:00.000Z</v>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L40" t="str">
+        <v>prod-metformin</v>
+      </c>
+      <c r="M40" t="str">
+        <v>Metformin Tablets</v>
+      </c>
+      <c r="N40" t="str">
+        <v>Antidiabetic</v>
+      </c>
+      <c r="O40" t="str">
+        <v>Ambient 15–30°C</v>
+      </c>
+      <c r="P40">
+        <v>15</v>
+      </c>
+      <c r="Q40">
+        <v>30</v>
+      </c>
+      <c r="R40" t="str">
+        <v>03000000000079</v>
+      </c>
+      <c r="S40" t="str">
+        <v>BN-2026-011</v>
+      </c>
+      <c r="T40" t="str">
+        <v>2026-03-09T12:00:00.000Z</v>
+      </c>
+      <c r="U40" t="str">
+        <v>2026-12-28T12:00:00.000Z</v>
+      </c>
+      <c r="V40" t="str">
+        <v>Generic Pharma Mumbai Ltd</v>
+      </c>
+      <c r="W40" t="str">
+        <v>India</v>
+      </c>
+      <c r="X40">
+        <v>24000</v>
+      </c>
+      <c r="Y40" t="str">
+        <v>car-h</v>
+      </c>
+      <c r="Z40" t="str">
+        <v>Global Air Freight</v>
+      </c>
+      <c r="AA40" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="AB40">
+        <v>75</v>
+      </c>
+      <c r="AC40">
+        <v>63</v>
+      </c>
+      <c r="AD40" t="str">
+        <v>loc-air-fra</v>
+      </c>
+      <c r="AE40" t="str">
+        <v>Frankfurt Air Cargo Hub</v>
+      </c>
+      <c r="AF40" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG40" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH40">
+        <v>50.0379</v>
+      </c>
+      <c r="AI40">
+        <v>8.5622</v>
+      </c>
+      <c r="AJ40" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK40" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL40" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM40" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN40">
+        <v>33.749</v>
+      </c>
+      <c r="AO40">
+        <v>-84.388</v>
+      </c>
+      <c r="AP40">
+        <v>5</v>
+      </c>
+      <c r="AQ40">
+        <v>6</v>
+      </c>
+      <c r="AR40">
+        <v>0</v>
+      </c>
+      <c r="AS40">
+        <v>2</v>
+      </c>
+      <c r="AT40" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU40">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="str">
+        <v/>
+      </c>
+      <c r="AW40" t="str">
+        <v/>
+      </c>
+      <c r="AX40" t="str">
+        <v/>
+      </c>
+      <c r="AY40">
+        <v>0</v>
+      </c>
+      <c r="AZ40">
+        <v>0</v>
+      </c>
+      <c r="BA40">
+        <v>0</v>
+      </c>
+      <c r="BB40">
+        <v>0</v>
+      </c>
+      <c r="BC40">
+        <v>0</v>
+      </c>
+      <c r="BD40">
+        <v>0</v>
+      </c>
+      <c r="BE40">
+        <v>0</v>
+      </c>
+      <c r="BF40">
+        <v>0</v>
+      </c>
+      <c r="BG40" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH40" t="str">
+        <v/>
+      </c>
+      <c r="BI40" t="str">
+        <v/>
+      </c>
+      <c r="BJ40" t="str">
+        <v/>
+      </c>
+      <c r="BK40" t="str">
+        <v/>
+      </c>
+      <c r="BL40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>SHP-040</v>
+      </c>
+      <c r="B41" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C41" t="str">
+        <v>TRUCK</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>2240</v>
+      </c>
+      <c r="F41" t="str">
+        <v>2026-06-20T12:00:00.000Z</v>
+      </c>
+      <c r="G41" t="str">
+        <v>2026-06-09T12:00:00.000Z</v>
+      </c>
+      <c r="H41" t="str">
+        <v>2026-06-09T12:00:00.000Z</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L41" t="str">
+        <v>prod-atorva</v>
+      </c>
+      <c r="M41" t="str">
+        <v>Atorvastatin Tablets</v>
+      </c>
+      <c r="N41" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="O41" t="str">
+        <v>Ambient 15–30°C</v>
+      </c>
+      <c r="P41">
+        <v>15</v>
+      </c>
+      <c r="Q41">
+        <v>30</v>
+      </c>
+      <c r="R41" t="str">
+        <v>03000000000062</v>
+      </c>
+      <c r="S41" t="str">
+        <v>BN-2026-004</v>
+      </c>
+      <c r="T41" t="str">
+        <v>2026-04-10T12:00:00.000Z</v>
+      </c>
+      <c r="U41" t="str">
+        <v>2027-11-12T12:00:00.000Z</v>
+      </c>
+      <c r="V41" t="str">
+        <v>Atlantic Pharmaceuticals</v>
+      </c>
+      <c r="W41" t="str">
+        <v>United States</v>
+      </c>
+      <c r="X41">
+        <v>20000</v>
+      </c>
+      <c r="Y41" t="str">
+        <v>car-b</v>
+      </c>
+      <c r="Z41" t="str">
+        <v>Carrier B Freight</v>
+      </c>
+      <c r="AA41" t="str">
+        <v>OCEAN | TRUCK</v>
+      </c>
+      <c r="AB41">
+        <v>50</v>
+      </c>
+      <c r="AC41">
+        <v>64</v>
+      </c>
+      <c r="AD41" t="str">
+        <v>loc-3pl-dallas</v>
+      </c>
+      <c r="AE41" t="str">
+        <v>3PL Warehouse — Dallas TX</v>
+      </c>
+      <c r="AF41" t="str">
+        <v>3PL</v>
+      </c>
+      <c r="AG41" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AH41">
+        <v>32.7767</v>
+      </c>
+      <c r="AI41">
+        <v>-96.797</v>
+      </c>
+      <c r="AJ41" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK41" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL41" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM41" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN41">
+        <v>40.7903</v>
+      </c>
+      <c r="AO41">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP41">
+        <v>3</v>
+      </c>
+      <c r="AQ41">
+        <v>6</v>
+      </c>
+      <c r="AR41">
+        <v>0</v>
+      </c>
+      <c r="AS41">
+        <v>2</v>
+      </c>
+      <c r="AT41" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU41">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="str">
+        <v/>
+      </c>
+      <c r="AW41" t="str">
+        <v/>
+      </c>
+      <c r="AX41" t="str">
+        <v/>
+      </c>
+      <c r="AY41">
+        <v>0</v>
+      </c>
+      <c r="AZ41">
+        <v>0</v>
+      </c>
+      <c r="BA41">
+        <v>0</v>
+      </c>
+      <c r="BB41">
+        <v>0</v>
+      </c>
+      <c r="BC41">
+        <v>0</v>
+      </c>
+      <c r="BD41">
+        <v>0</v>
+      </c>
+      <c r="BE41">
+        <v>0</v>
+      </c>
+      <c r="BF41">
+        <v>0</v>
+      </c>
+      <c r="BG41" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH41" t="str">
+        <v/>
+      </c>
+      <c r="BI41" t="str">
+        <v/>
+      </c>
+      <c r="BJ41" t="str">
+        <v/>
+      </c>
+      <c r="BK41" t="str">
+        <v/>
+      </c>
+      <c r="BL41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>SHP-041</v>
+      </c>
+      <c r="B42" t="str">
+        <v>DELAYED</v>
+      </c>
+      <c r="C42" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D42">
+        <v>14</v>
+      </c>
+      <c r="E42">
+        <v>1522</v>
+      </c>
+      <c r="F42" t="str">
+        <v>2026-06-21T12:00:00.000Z</v>
+      </c>
+      <c r="G42" t="str">
+        <v>2026-07-01T12:00:00.000Z</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="b">
+        <v>1</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L42" t="str">
+        <v>prod-salbutamol</v>
+      </c>
+      <c r="M42" t="str">
+        <v>Salbutamol Inhaler</v>
+      </c>
+      <c r="N42" t="str">
+        <v>Respiratory</v>
+      </c>
+      <c r="O42" t="str">
+        <v>Controlled room 15–25°C</v>
+      </c>
+      <c r="P42">
+        <v>15</v>
+      </c>
+      <c r="Q42">
+        <v>25</v>
+      </c>
+      <c r="R42" t="str">
+        <v>03000000000109</v>
+      </c>
+      <c r="S42" t="str">
+        <v>BN-2026-019</v>
+      </c>
+      <c r="T42" t="str">
+        <v>2026-04-27T12:00:00.000Z</v>
+      </c>
+      <c r="U42" t="str">
+        <v>2027-12-08T12:00:00.000Z</v>
+      </c>
+      <c r="V42" t="str">
+        <v>Pacific Biologics Co</v>
+      </c>
+      <c r="W42" t="str">
+        <v>China</v>
+      </c>
+      <c r="X42">
+        <v>30000</v>
+      </c>
+      <c r="Y42" t="str">
+        <v>car-c</v>
+      </c>
+      <c r="Z42" t="str">
+        <v>SkyCargo Air</v>
+      </c>
+      <c r="AA42" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="AB42">
+        <v>33</v>
+      </c>
+      <c r="AC42">
+        <v>48</v>
+      </c>
+      <c r="AD42" t="str">
+        <v>loc-air-lhr</v>
+      </c>
+      <c r="AE42" t="str">
+        <v>Heathrow Air Cargo Hub</v>
+      </c>
+      <c r="AF42" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG42" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="AH42">
+        <v>51.47</v>
+      </c>
+      <c r="AI42">
+        <v>-0.4543</v>
+      </c>
+      <c r="AJ42" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK42" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL42" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM42" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN42">
+        <v>33.749</v>
+      </c>
+      <c r="AO42">
+        <v>-84.388</v>
+      </c>
+      <c r="AP42">
+        <v>5</v>
+      </c>
+      <c r="AQ42">
+        <v>6</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>2</v>
+      </c>
+      <c r="AT42" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU42">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="str">
+        <v/>
+      </c>
+      <c r="AW42" t="str">
+        <v/>
+      </c>
+      <c r="AX42" t="str">
+        <v/>
+      </c>
+      <c r="AY42">
+        <v>0</v>
+      </c>
+      <c r="AZ42">
+        <v>1</v>
+      </c>
+      <c r="BA42">
+        <v>1</v>
+      </c>
+      <c r="BB42">
+        <v>1</v>
+      </c>
+      <c r="BC42">
+        <v>0</v>
+      </c>
+      <c r="BD42">
+        <v>0</v>
+      </c>
+      <c r="BE42">
+        <v>0</v>
+      </c>
+      <c r="BF42">
+        <v>0</v>
+      </c>
+      <c r="BG42" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH42" t="str">
+        <v/>
+      </c>
+      <c r="BI42" t="str">
+        <v/>
+      </c>
+      <c r="BJ42" t="str">
+        <v/>
+      </c>
+      <c r="BK42" t="str">
+        <v/>
+      </c>
+      <c r="BL42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>SHP-042</v>
+      </c>
+      <c r="B43" t="str">
+        <v>IN_TRANSIT</v>
+      </c>
+      <c r="C43" t="str">
+        <v>TRUCK</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>1115</v>
+      </c>
+      <c r="F43" t="str">
+        <v>2026-06-17T12:00:00.000Z</v>
+      </c>
+      <c r="G43" t="str">
+        <v>2026-07-06T12:00:00.000Z</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="b">
+        <v>1</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L43" t="str">
+        <v>prod-atorva</v>
+      </c>
+      <c r="M43" t="str">
+        <v>Atorvastatin Tablets</v>
+      </c>
+      <c r="N43" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="O43" t="str">
+        <v>Ambient 15–30°C</v>
+      </c>
+      <c r="P43">
+        <v>15</v>
+      </c>
+      <c r="Q43">
+        <v>30</v>
+      </c>
+      <c r="R43" t="str">
+        <v>03000000000062</v>
+      </c>
+      <c r="S43" t="str">
+        <v>BN-2026-004</v>
+      </c>
+      <c r="T43" t="str">
+        <v>2026-04-10T12:00:00.000Z</v>
+      </c>
+      <c r="U43" t="str">
+        <v>2027-11-12T12:00:00.000Z</v>
+      </c>
+      <c r="V43" t="str">
+        <v>Atlantic Pharmaceuticals</v>
+      </c>
+      <c r="W43" t="str">
+        <v>United States</v>
+      </c>
+      <c r="X43">
+        <v>20000</v>
+      </c>
+      <c r="Y43" t="str">
+        <v>car-f</v>
+      </c>
+      <c r="Z43" t="str">
+        <v>EuroRail Logistics</v>
+      </c>
+      <c r="AA43" t="str">
+        <v>RAIL | TRUCK</v>
+      </c>
+      <c r="AB43">
+        <v>100</v>
+      </c>
+      <c r="AC43">
+        <v>62</v>
+      </c>
+      <c r="AD43" t="str">
+        <v>loc-3pl-dallas</v>
+      </c>
+      <c r="AE43" t="str">
+        <v>3PL Warehouse — Dallas TX</v>
+      </c>
+      <c r="AF43" t="str">
+        <v>3PL</v>
+      </c>
+      <c r="AG43" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AH43">
+        <v>32.7767</v>
+      </c>
+      <c r="AI43">
+        <v>-96.797</v>
+      </c>
+      <c r="AJ43" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK43" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL43" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM43" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN43">
+        <v>40.7903</v>
+      </c>
+      <c r="AO43">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP43">
+        <v>3</v>
+      </c>
+      <c r="AQ43">
+        <v>6</v>
+      </c>
+      <c r="AR43">
+        <v>0</v>
+      </c>
+      <c r="AS43">
+        <v>2</v>
+      </c>
+      <c r="AT43" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU43">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="str">
+        <v/>
+      </c>
+      <c r="AW43" t="str">
+        <v/>
+      </c>
+      <c r="AX43" t="str">
+        <v/>
+      </c>
+      <c r="AY43">
+        <v>0</v>
+      </c>
+      <c r="AZ43">
+        <v>0</v>
+      </c>
+      <c r="BA43">
+        <v>0</v>
+      </c>
+      <c r="BB43">
+        <v>0</v>
+      </c>
+      <c r="BC43">
+        <v>0</v>
+      </c>
+      <c r="BD43">
+        <v>0</v>
+      </c>
+      <c r="BE43">
+        <v>0</v>
+      </c>
+      <c r="BF43">
+        <v>0</v>
+      </c>
+      <c r="BG43" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH43" t="str">
+        <v/>
+      </c>
+      <c r="BI43" t="str">
+        <v/>
+      </c>
+      <c r="BJ43" t="str">
+        <v/>
+      </c>
+      <c r="BK43" t="str">
+        <v/>
+      </c>
+      <c r="BL43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>SHP-043</v>
+      </c>
+      <c r="B44" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C44" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D44">
+        <v>14</v>
+      </c>
+      <c r="E44">
+        <v>2258</v>
+      </c>
+      <c r="F44" t="str">
+        <v>2026-06-16T12:00:00.000Z</v>
+      </c>
+      <c r="G44" t="str">
+        <v>2026-06-19T22:00:00.000Z</v>
+      </c>
+      <c r="H44" t="str">
+        <v>2026-06-20T12:00:00.000Z</v>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="b">
+        <v>1</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L44" t="str">
+        <v>prod-omeprazole</v>
+      </c>
+      <c r="M44" t="str">
+        <v>Omeprazole Capsules</v>
+      </c>
+      <c r="N44" t="str">
+        <v>Gastrointestinal</v>
+      </c>
+      <c r="O44" t="str">
+        <v>Ambient 15–25°C</v>
+      </c>
+      <c r="P44">
+        <v>15</v>
+      </c>
+      <c r="Q44">
+        <v>25</v>
+      </c>
+      <c r="R44" t="str">
+        <v>03000000000093</v>
+      </c>
+      <c r="S44" t="str">
+        <v>BN-2026-013</v>
+      </c>
+      <c r="T44" t="str">
+        <v>2026-05-31T12:00:00.000Z</v>
+      </c>
+      <c r="U44" t="str">
+        <v>2028-01-27T12:00:00.000Z</v>
+      </c>
+      <c r="V44" t="str">
+        <v>EuroPharma Manufacturing</v>
+      </c>
+      <c r="W44" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="X44">
+        <v>39000</v>
+      </c>
+      <c r="Y44" t="str">
+        <v>car-c</v>
+      </c>
+      <c r="Z44" t="str">
+        <v>SkyCargo Air</v>
+      </c>
+      <c r="AA44" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="AB44">
+        <v>33</v>
+      </c>
+      <c r="AC44">
+        <v>48</v>
+      </c>
+      <c r="AD44" t="str">
+        <v>loc-air-lhr</v>
+      </c>
+      <c r="AE44" t="str">
+        <v>Heathrow Air Cargo Hub</v>
+      </c>
+      <c r="AF44" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG44" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="AH44">
+        <v>51.47</v>
+      </c>
+      <c r="AI44">
+        <v>-0.4543</v>
+      </c>
+      <c r="AJ44" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK44" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL44" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM44" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN44">
+        <v>33.749</v>
+      </c>
+      <c r="AO44">
+        <v>-84.388</v>
+      </c>
+      <c r="AP44">
+        <v>5</v>
+      </c>
+      <c r="AQ44">
+        <v>6</v>
+      </c>
+      <c r="AR44">
+        <v>0</v>
+      </c>
+      <c r="AS44">
+        <v>2</v>
+      </c>
+      <c r="AT44" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU44">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="str">
+        <v/>
+      </c>
+      <c r="AW44" t="str">
+        <v/>
+      </c>
+      <c r="AX44" t="str">
+        <v/>
+      </c>
+      <c r="AY44">
+        <v>0</v>
+      </c>
+      <c r="AZ44">
+        <v>0</v>
+      </c>
+      <c r="BA44">
+        <v>0</v>
+      </c>
+      <c r="BB44">
+        <v>0</v>
+      </c>
+      <c r="BC44">
+        <v>0</v>
+      </c>
+      <c r="BD44">
+        <v>0</v>
+      </c>
+      <c r="BE44">
+        <v>0</v>
+      </c>
+      <c r="BF44">
+        <v>0</v>
+      </c>
+      <c r="BG44" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH44" t="str">
+        <v/>
+      </c>
+      <c r="BI44" t="str">
+        <v/>
+      </c>
+      <c r="BJ44" t="str">
+        <v/>
+      </c>
+      <c r="BK44" t="str">
+        <v/>
+      </c>
+      <c r="BL44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>SHP-044</v>
+      </c>
+      <c r="B45" t="str">
+        <v>DELAYED</v>
+      </c>
+      <c r="C45" t="str">
+        <v>TRUCK</v>
+      </c>
+      <c r="D45">
+        <v>26</v>
+      </c>
+      <c r="E45">
+        <v>2263</v>
+      </c>
+      <c r="F45" t="str">
+        <v>2026-06-19T12:00:00.000Z</v>
+      </c>
+      <c r="G45" t="str">
+        <v>2026-07-01T12:00:00.000Z</v>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="b">
+        <v>1</v>
+      </c>
+      <c r="K45" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L45" t="str">
+        <v>prod-atorva</v>
+      </c>
+      <c r="M45" t="str">
+        <v>Atorvastatin Tablets</v>
+      </c>
+      <c r="N45" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="O45" t="str">
+        <v>Ambient 15–30°C</v>
+      </c>
+      <c r="P45">
+        <v>15</v>
+      </c>
+      <c r="Q45">
+        <v>30</v>
+      </c>
+      <c r="R45" t="str">
+        <v>03000000000062</v>
+      </c>
+      <c r="S45" t="str">
+        <v>BN-2026-004</v>
+      </c>
+      <c r="T45" t="str">
+        <v>2026-04-10T12:00:00.000Z</v>
+      </c>
+      <c r="U45" t="str">
+        <v>2027-11-12T12:00:00.000Z</v>
+      </c>
+      <c r="V45" t="str">
+        <v>Atlantic Pharmaceuticals</v>
+      </c>
+      <c r="W45" t="str">
+        <v>United States</v>
+      </c>
+      <c r="X45">
+        <v>20000</v>
+      </c>
+      <c r="Y45" t="str">
+        <v>car-f</v>
+      </c>
+      <c r="Z45" t="str">
+        <v>EuroRail Logistics</v>
+      </c>
+      <c r="AA45" t="str">
+        <v>RAIL | TRUCK</v>
+      </c>
+      <c r="AB45">
+        <v>100</v>
+      </c>
+      <c r="AC45">
+        <v>62</v>
+      </c>
+      <c r="AD45" t="str">
+        <v>loc-3pl-nj</v>
+      </c>
+      <c r="AE45" t="str">
+        <v>3PL Warehouse — Edison NJ</v>
+      </c>
+      <c r="AF45" t="str">
+        <v>3PL</v>
+      </c>
+      <c r="AG45" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AH45">
+        <v>40.5187</v>
+      </c>
+      <c r="AI45">
+        <v>-74.4121</v>
+      </c>
+      <c r="AJ45" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK45" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL45" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM45" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN45">
+        <v>33.749</v>
+      </c>
+      <c r="AO45">
+        <v>-84.388</v>
+      </c>
+      <c r="AP45">
+        <v>3</v>
+      </c>
+      <c r="AQ45">
+        <v>6</v>
+      </c>
+      <c r="AR45">
+        <v>0</v>
+      </c>
+      <c r="AS45">
+        <v>2</v>
+      </c>
+      <c r="AT45" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU45">
+        <v>0</v>
+      </c>
+      <c r="AV45" t="str">
+        <v/>
+      </c>
+      <c r="AW45" t="str">
+        <v/>
+      </c>
+      <c r="AX45" t="str">
+        <v/>
+      </c>
+      <c r="AY45">
+        <v>0</v>
+      </c>
+      <c r="AZ45">
+        <v>1</v>
+      </c>
+      <c r="BA45">
+        <v>1</v>
+      </c>
+      <c r="BB45">
+        <v>1</v>
+      </c>
+      <c r="BC45">
+        <v>0</v>
+      </c>
+      <c r="BD45">
+        <v>0</v>
+      </c>
+      <c r="BE45">
+        <v>0</v>
+      </c>
+      <c r="BF45">
+        <v>0</v>
+      </c>
+      <c r="BG45" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH45" t="str">
+        <v/>
+      </c>
+      <c r="BI45" t="str">
+        <v/>
+      </c>
+      <c r="BJ45" t="str">
+        <v/>
+      </c>
+      <c r="BK45" t="str">
+        <v/>
+      </c>
+      <c r="BL45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>SHP-045</v>
+      </c>
+      <c r="B46" t="str">
+        <v>DELAYED</v>
+      </c>
+      <c r="C46" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D46">
+        <v>11</v>
+      </c>
+      <c r="E46">
+        <v>902</v>
+      </c>
+      <c r="F46" t="str">
+        <v>2026-06-23T12:00:00.000Z</v>
+      </c>
+      <c r="G46" t="str">
+        <v>2026-07-01T12:00:00.000Z</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="b">
+        <v>1</v>
+      </c>
+      <c r="K46" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L46" t="str">
+        <v>prod-metformin</v>
+      </c>
+      <c r="M46" t="str">
+        <v>Metformin Tablets</v>
+      </c>
+      <c r="N46" t="str">
+        <v>Antidiabetic</v>
+      </c>
+      <c r="O46" t="str">
+        <v>Ambient 15–30°C</v>
+      </c>
+      <c r="P46">
+        <v>15</v>
+      </c>
+      <c r="Q46">
+        <v>30</v>
+      </c>
+      <c r="R46" t="str">
+        <v>03000000000079</v>
+      </c>
+      <c r="S46" t="str">
+        <v>BN-2026-011</v>
+      </c>
+      <c r="T46" t="str">
+        <v>2026-03-09T12:00:00.000Z</v>
+      </c>
+      <c r="U46" t="str">
+        <v>2026-12-28T12:00:00.000Z</v>
+      </c>
+      <c r="V46" t="str">
+        <v>Generic Pharma Mumbai Ltd</v>
+      </c>
+      <c r="W46" t="str">
+        <v>India</v>
+      </c>
+      <c r="X46">
+        <v>24000</v>
+      </c>
+      <c r="Y46" t="str">
+        <v>car-c</v>
+      </c>
+      <c r="Z46" t="str">
+        <v>SkyCargo Air</v>
+      </c>
+      <c r="AA46" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="AB46">
+        <v>33</v>
+      </c>
+      <c r="AC46">
+        <v>48</v>
+      </c>
+      <c r="AD46" t="str">
+        <v>loc-air-fra</v>
+      </c>
+      <c r="AE46" t="str">
+        <v>Frankfurt Air Cargo Hub</v>
+      </c>
+      <c r="AF46" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG46" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH46">
+        <v>50.0379</v>
+      </c>
+      <c r="AI46">
+        <v>8.5622</v>
+      </c>
+      <c r="AJ46" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK46" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL46" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM46" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN46">
+        <v>33.749</v>
+      </c>
+      <c r="AO46">
+        <v>-84.388</v>
+      </c>
+      <c r="AP46">
+        <v>5</v>
+      </c>
+      <c r="AQ46">
+        <v>6</v>
+      </c>
+      <c r="AR46">
+        <v>0</v>
+      </c>
+      <c r="AS46">
+        <v>2</v>
+      </c>
+      <c r="AT46" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU46">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="str">
+        <v/>
+      </c>
+      <c r="AW46" t="str">
+        <v/>
+      </c>
+      <c r="AX46" t="str">
+        <v/>
+      </c>
+      <c r="AY46">
+        <v>0</v>
+      </c>
+      <c r="AZ46">
+        <v>1</v>
+      </c>
+      <c r="BA46">
+        <v>1</v>
+      </c>
+      <c r="BB46">
+        <v>1</v>
+      </c>
+      <c r="BC46">
+        <v>0</v>
+      </c>
+      <c r="BD46">
+        <v>0</v>
+      </c>
+      <c r="BE46">
+        <v>0</v>
+      </c>
+      <c r="BF46">
+        <v>0</v>
+      </c>
+      <c r="BG46" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH46" t="str">
+        <v/>
+      </c>
+      <c r="BI46" t="str">
+        <v/>
+      </c>
+      <c r="BJ46" t="str">
+        <v/>
+      </c>
+      <c r="BK46" t="str">
+        <v/>
+      </c>
+      <c r="BL46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>SHP-046</v>
+      </c>
+      <c r="B47" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C47" t="str">
+        <v>TRUCK</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>294</v>
+      </c>
+      <c r="F47" t="str">
+        <v>2026-06-21T12:00:00.000Z</v>
+      </c>
+      <c r="G47" t="str">
+        <v>2026-06-10T12:00:00.000Z</v>
+      </c>
+      <c r="H47" t="str">
+        <v>2026-06-10T12:00:00.000Z</v>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="b">
+        <v>1</v>
+      </c>
+      <c r="K47" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L47" t="str">
+        <v>prod-ibuprofen</v>
+      </c>
+      <c r="M47" t="str">
+        <v>Ibuprofen Tablets</v>
+      </c>
+      <c r="N47" t="str">
+        <v>Analgesic</v>
+      </c>
+      <c r="O47" t="str">
+        <v>Ambient 15–25°C</v>
+      </c>
+      <c r="P47">
+        <v>15</v>
+      </c>
+      <c r="Q47">
+        <v>25</v>
+      </c>
+      <c r="R47" t="str">
+        <v>03000000000086</v>
+      </c>
+      <c r="S47" t="str">
+        <v>BN-2026-018</v>
+      </c>
+      <c r="T47" t="str">
+        <v>2026-03-20T12:00:00.000Z</v>
+      </c>
+      <c r="U47" t="str">
+        <v>2028-02-27T12:00:00.000Z</v>
+      </c>
+      <c r="V47" t="str">
+        <v>EuroPharma Manufacturing</v>
+      </c>
+      <c r="W47" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="X47">
+        <v>27000</v>
+      </c>
+      <c r="Y47" t="str">
+        <v>car-f</v>
+      </c>
+      <c r="Z47" t="str">
+        <v>EuroRail Logistics</v>
+      </c>
+      <c r="AA47" t="str">
+        <v>RAIL | TRUCK</v>
+      </c>
+      <c r="AB47">
+        <v>100</v>
+      </c>
+      <c r="AC47">
+        <v>62</v>
+      </c>
+      <c r="AD47" t="str">
+        <v>loc-3pl-dallas</v>
+      </c>
+      <c r="AE47" t="str">
+        <v>3PL Warehouse — Dallas TX</v>
+      </c>
+      <c r="AF47" t="str">
+        <v>3PL</v>
+      </c>
+      <c r="AG47" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AH47">
+        <v>32.7767</v>
+      </c>
+      <c r="AI47">
+        <v>-96.797</v>
+      </c>
+      <c r="AJ47" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK47" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL47" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM47" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN47">
+        <v>33.749</v>
+      </c>
+      <c r="AO47">
+        <v>-84.388</v>
+      </c>
+      <c r="AP47">
+        <v>3</v>
+      </c>
+      <c r="AQ47">
+        <v>6</v>
+      </c>
+      <c r="AR47">
+        <v>0</v>
+      </c>
+      <c r="AS47">
+        <v>2</v>
+      </c>
+      <c r="AT47" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU47">
+        <v>0</v>
+      </c>
+      <c r="AV47" t="str">
+        <v/>
+      </c>
+      <c r="AW47" t="str">
+        <v/>
+      </c>
+      <c r="AX47" t="str">
+        <v/>
+      </c>
+      <c r="AY47">
+        <v>0</v>
+      </c>
+      <c r="AZ47">
+        <v>0</v>
+      </c>
+      <c r="BA47">
+        <v>0</v>
+      </c>
+      <c r="BB47">
+        <v>0</v>
+      </c>
+      <c r="BC47">
+        <v>0</v>
+      </c>
+      <c r="BD47">
+        <v>0</v>
+      </c>
+      <c r="BE47">
+        <v>0</v>
+      </c>
+      <c r="BF47">
+        <v>0</v>
+      </c>
+      <c r="BG47" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH47" t="str">
+        <v/>
+      </c>
+      <c r="BI47" t="str">
+        <v/>
+      </c>
+      <c r="BJ47" t="str">
+        <v/>
+      </c>
+      <c r="BK47" t="str">
+        <v/>
+      </c>
+      <c r="BL47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>SHP-047</v>
+      </c>
+      <c r="B48" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C48" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>2076</v>
+      </c>
+      <c r="F48" t="str">
+        <v>2026-06-18T12:00:00.000Z</v>
+      </c>
+      <c r="G48" t="str">
+        <v>2026-06-05T12:00:00.000Z</v>
+      </c>
+      <c r="H48" t="str">
+        <v>2026-06-05T12:00:00.000Z</v>
+      </c>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="b">
+        <v>1</v>
+      </c>
+      <c r="K48" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L48" t="str">
+        <v>prod-insulin</v>
+      </c>
+      <c r="M48" t="str">
+        <v>Insulin Glargine Injection</v>
+      </c>
+      <c r="N48" t="str">
+        <v>Biologic (Antidiabetic)</v>
+      </c>
+      <c r="O48" t="str">
+        <v>Cold chain 2–8°C</v>
+      </c>
+      <c r="P48">
+        <v>2</v>
+      </c>
+      <c r="Q48">
+        <v>8</v>
+      </c>
+      <c r="R48" t="str">
+        <v>03000000000024</v>
+      </c>
+      <c r="S48" t="str">
+        <v>BN-2026-012</v>
+      </c>
+      <c r="T48" t="str">
+        <v>2026-05-19T12:00:00.000Z</v>
+      </c>
+      <c r="U48" t="str">
+        <v>2027-04-15T12:00:00.000Z</v>
+      </c>
+      <c r="V48" t="str">
+        <v>BioNTech Marburg GmbH</v>
+      </c>
+      <c r="W48" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="X48">
+        <v>4000</v>
+      </c>
+      <c r="Y48" t="str">
+        <v>car-c</v>
+      </c>
+      <c r="Z48" t="str">
+        <v>SkyCargo Air</v>
+      </c>
+      <c r="AA48" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="AB48">
+        <v>33</v>
+      </c>
+      <c r="AC48">
+        <v>48</v>
+      </c>
+      <c r="AD48" t="str">
+        <v>loc-air-lhr</v>
+      </c>
+      <c r="AE48" t="str">
+        <v>Heathrow Air Cargo Hub</v>
+      </c>
+      <c r="AF48" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG48" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="AH48">
+        <v>51.47</v>
+      </c>
+      <c r="AI48">
+        <v>-0.4543</v>
+      </c>
+      <c r="AJ48" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK48" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL48" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM48" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN48">
+        <v>40.7903</v>
+      </c>
+      <c r="AO48">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP48">
+        <v>5</v>
+      </c>
+      <c r="AQ48">
+        <v>6</v>
+      </c>
+      <c r="AR48">
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>2</v>
+      </c>
+      <c r="AT48" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU48">
+        <v>0</v>
+      </c>
+      <c r="AV48" t="str">
+        <v/>
+      </c>
+      <c r="AW48" t="str">
+        <v/>
+      </c>
+      <c r="AX48" t="str">
+        <v/>
+      </c>
+      <c r="AY48">
+        <v>0</v>
+      </c>
+      <c r="AZ48">
+        <v>1</v>
+      </c>
+      <c r="BA48">
+        <v>1</v>
+      </c>
+      <c r="BB48">
+        <v>0</v>
+      </c>
+      <c r="BC48">
+        <v>1</v>
+      </c>
+      <c r="BD48">
+        <v>0</v>
+      </c>
+      <c r="BE48">
+        <v>0</v>
+      </c>
+      <c r="BF48">
+        <v>0</v>
+      </c>
+      <c r="BG48" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH48" t="str">
+        <v/>
+      </c>
+      <c r="BI48" t="str">
+        <v/>
+      </c>
+      <c r="BJ48" t="str">
+        <v/>
+      </c>
+      <c r="BK48" t="str">
+        <v/>
+      </c>
+      <c r="BL48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>SHP-048</v>
+      </c>
+      <c r="B49" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C49" t="str">
+        <v>TRUCK</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>2114</v>
+      </c>
+      <c r="F49" t="str">
+        <v>2026-06-22T12:00:00.000Z</v>
+      </c>
+      <c r="G49" t="str">
+        <v>2026-06-15T12:00:00.000Z</v>
+      </c>
+      <c r="H49" t="str">
+        <v>2026-06-15T12:00:00.000Z</v>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="b">
+        <v>1</v>
+      </c>
+      <c r="K49" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="L49" t="str">
+        <v>prod-mab</v>
+      </c>
+      <c r="M49" t="str">
+        <v>Monoclonal Antibody Infusion</v>
+      </c>
+      <c r="N49" t="str">
+        <v>Biologic (Oncology)</v>
+      </c>
+      <c r="O49" t="str">
+        <v>Cold chain 2–8°C</v>
+      </c>
+      <c r="P49">
+        <v>2</v>
+      </c>
+      <c r="Q49">
+        <v>8</v>
+      </c>
+      <c r="R49" t="str">
+        <v>03000000000031</v>
+      </c>
+      <c r="S49" t="str">
+        <v>BN-2026-017</v>
+      </c>
+      <c r="T49" t="str">
+        <v>2026-04-26T12:00:00.000Z</v>
+      </c>
+      <c r="U49" t="str">
+        <v>2027-07-18T12:00:00.000Z</v>
+      </c>
+      <c r="V49" t="str">
+        <v>EuroPharma Manufacturing</v>
+      </c>
+      <c r="W49" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="X49">
+        <v>32000</v>
+      </c>
+      <c r="Y49" t="str">
+        <v>car-d</v>
+      </c>
+      <c r="Z49" t="str">
+        <v>TransContinental Trucking</v>
+      </c>
+      <c r="AA49" t="str">
+        <v>TRUCK</v>
+      </c>
+      <c r="AB49">
+        <v>50</v>
+      </c>
+      <c r="AC49">
+        <v>52</v>
+      </c>
+      <c r="AD49" t="str">
+        <v>loc-3pl-dallas</v>
+      </c>
+      <c r="AE49" t="str">
+        <v>3PL Warehouse — Dallas TX</v>
+      </c>
+      <c r="AF49" t="str">
+        <v>3PL</v>
+      </c>
+      <c r="AG49" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AH49">
+        <v>32.7767</v>
+      </c>
+      <c r="AI49">
+        <v>-96.797</v>
+      </c>
+      <c r="AJ49" t="str">
+        <v>loc-hospital-ny</v>
+      </c>
+      <c r="AK49" t="str">
+        <v>Mount Sinai Hospital Network — New York</v>
+      </c>
+      <c r="AL49" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM49" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN49">
+        <v>40.7903</v>
+      </c>
+      <c r="AO49">
+        <v>-73.9527</v>
+      </c>
+      <c r="AP49">
+        <v>3</v>
+      </c>
+      <c r="AQ49">
+        <v>6</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>2</v>
+      </c>
+      <c r="AT49" t="str">
+        <v>BioNTech Marburg GmbH → Northeast Pharma Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU49">
+        <v>0</v>
+      </c>
+      <c r="AV49" t="str">
+        <v/>
+      </c>
+      <c r="AW49" t="str">
+        <v/>
+      </c>
+      <c r="AX49" t="str">
+        <v/>
+      </c>
+      <c r="AY49">
+        <v>0</v>
+      </c>
+      <c r="AZ49">
+        <v>0</v>
+      </c>
+      <c r="BA49">
+        <v>0</v>
+      </c>
+      <c r="BB49">
+        <v>0</v>
+      </c>
+      <c r="BC49">
+        <v>0</v>
+      </c>
+      <c r="BD49">
+        <v>0</v>
+      </c>
+      <c r="BE49">
+        <v>0</v>
+      </c>
+      <c r="BF49">
+        <v>0</v>
+      </c>
+      <c r="BG49" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH49" t="str">
+        <v/>
+      </c>
+      <c r="BI49" t="str">
+        <v/>
+      </c>
+      <c r="BJ49" t="str">
+        <v/>
+      </c>
+      <c r="BK49" t="str">
+        <v/>
+      </c>
+      <c r="BL49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>SHP-049</v>
+      </c>
+      <c r="B50" t="str">
+        <v>DELIVERED</v>
+      </c>
+      <c r="C50" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>808</v>
+      </c>
+      <c r="F50" t="str">
+        <v>2026-06-20T12:00:00.000Z</v>
+      </c>
+      <c r="G50" t="str">
+        <v>2026-06-05T12:00:00.000Z</v>
+      </c>
+      <c r="H50" t="str">
+        <v>2026-06-05T12:00:00.000Z</v>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="b">
+        <v>1</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L50" t="str">
+        <v>prod-ibuprofen</v>
+      </c>
+      <c r="M50" t="str">
+        <v>Ibuprofen Tablets</v>
+      </c>
+      <c r="N50" t="str">
+        <v>Analgesic</v>
+      </c>
+      <c r="O50" t="str">
+        <v>Ambient 15–25°C</v>
+      </c>
+      <c r="P50">
+        <v>15</v>
+      </c>
+      <c r="Q50">
+        <v>25</v>
+      </c>
+      <c r="R50" t="str">
+        <v>03000000000086</v>
+      </c>
+      <c r="S50" t="str">
+        <v>BN-2026-018</v>
+      </c>
+      <c r="T50" t="str">
+        <v>2026-03-20T12:00:00.000Z</v>
+      </c>
+      <c r="U50" t="str">
+        <v>2028-02-27T12:00:00.000Z</v>
+      </c>
+      <c r="V50" t="str">
+        <v>EuroPharma Manufacturing</v>
+      </c>
+      <c r="W50" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="X50">
+        <v>27000</v>
+      </c>
+      <c r="Y50" t="str">
+        <v>car-h</v>
+      </c>
+      <c r="Z50" t="str">
+        <v>Global Air Freight</v>
+      </c>
+      <c r="AA50" t="str">
+        <v>AIR</v>
+      </c>
+      <c r="AB50">
+        <v>75</v>
+      </c>
+      <c r="AC50">
+        <v>63</v>
+      </c>
+      <c r="AD50" t="str">
+        <v>loc-air-fra</v>
+      </c>
+      <c r="AE50" t="str">
+        <v>Frankfurt Air Cargo Hub</v>
+      </c>
+      <c r="AF50" t="str">
+        <v>PORT</v>
+      </c>
+      <c r="AG50" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="AH50">
+        <v>50.0379</v>
+      </c>
+      <c r="AI50">
+        <v>8.5622</v>
+      </c>
+      <c r="AJ50" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK50" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL50" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM50" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN50">
+        <v>33.749</v>
+      </c>
+      <c r="AO50">
+        <v>-84.388</v>
+      </c>
+      <c r="AP50">
+        <v>5</v>
+      </c>
+      <c r="AQ50">
+        <v>6</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>2</v>
+      </c>
+      <c r="AT50" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU50">
+        <v>0</v>
+      </c>
+      <c r="AV50" t="str">
+        <v/>
+      </c>
+      <c r="AW50" t="str">
+        <v/>
+      </c>
+      <c r="AX50" t="str">
+        <v/>
+      </c>
+      <c r="AY50">
+        <v>0</v>
+      </c>
+      <c r="AZ50">
+        <v>0</v>
+      </c>
+      <c r="BA50">
+        <v>0</v>
+      </c>
+      <c r="BB50">
+        <v>0</v>
+      </c>
+      <c r="BC50">
+        <v>0</v>
+      </c>
+      <c r="BD50">
+        <v>0</v>
+      </c>
+      <c r="BE50">
+        <v>0</v>
+      </c>
+      <c r="BF50">
+        <v>0</v>
+      </c>
+      <c r="BG50" t="str">
+        <v>Customs Congestion — Newark | Heatwave — US Northeast</v>
+      </c>
+      <c r="BH50" t="str">
+        <v/>
+      </c>
+      <c r="BI50" t="str">
+        <v/>
+      </c>
+      <c r="BJ50" t="str">
+        <v/>
+      </c>
+      <c r="BK50" t="str">
+        <v/>
+      </c>
+      <c r="BL50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>SHP-050</v>
+      </c>
+      <c r="B51" t="str">
+        <v>IN_TRANSIT</v>
+      </c>
+      <c r="C51" t="str">
+        <v>TRUCK</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>558</v>
+      </c>
+      <c r="F51" t="str">
+        <v>2026-06-19T12:00:00.000Z</v>
+      </c>
+      <c r="G51" t="str">
+        <v>2026-06-28T12:00:00.000Z</v>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="L51" t="str">
+        <v>prod-metformin</v>
+      </c>
+      <c r="M51" t="str">
+        <v>Metformin Tablets</v>
+      </c>
+      <c r="N51" t="str">
+        <v>Antidiabetic</v>
+      </c>
+      <c r="O51" t="str">
+        <v>Ambient 15–30°C</v>
+      </c>
+      <c r="P51">
+        <v>15</v>
+      </c>
+      <c r="Q51">
+        <v>30</v>
+      </c>
+      <c r="R51" t="str">
+        <v>03000000000079</v>
+      </c>
+      <c r="S51" t="str">
+        <v>BN-2026-011</v>
+      </c>
+      <c r="T51" t="str">
+        <v>2026-03-09T12:00:00.000Z</v>
+      </c>
+      <c r="U51" t="str">
+        <v>2026-12-28T12:00:00.000Z</v>
+      </c>
+      <c r="V51" t="str">
+        <v>Generic Pharma Mumbai Ltd</v>
+      </c>
+      <c r="W51" t="str">
+        <v>India</v>
+      </c>
+      <c r="X51">
+        <v>24000</v>
+      </c>
+      <c r="Y51" t="str">
+        <v>car-b</v>
+      </c>
+      <c r="Z51" t="str">
+        <v>Carrier B Freight</v>
+      </c>
+      <c r="AA51" t="str">
+        <v>OCEAN | TRUCK</v>
+      </c>
+      <c r="AB51">
+        <v>50</v>
+      </c>
+      <c r="AC51">
+        <v>64</v>
+      </c>
+      <c r="AD51" t="str">
+        <v>loc-3pl-dallas</v>
+      </c>
+      <c r="AE51" t="str">
+        <v>3PL Warehouse — Dallas TX</v>
+      </c>
+      <c r="AF51" t="str">
+        <v>3PL</v>
+      </c>
+      <c r="AG51" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AH51">
+        <v>32.7767</v>
+      </c>
+      <c r="AI51">
+        <v>-96.797</v>
+      </c>
+      <c r="AJ51" t="str">
+        <v>loc-hospital-atl</v>
+      </c>
+      <c r="AK51" t="str">
+        <v>Emory Hospital Network — Atlanta</v>
+      </c>
+      <c r="AL51" t="str">
+        <v>HOSPITAL</v>
+      </c>
+      <c r="AM51" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AN51">
+        <v>33.749</v>
+      </c>
+      <c r="AO51">
+        <v>-84.388</v>
+      </c>
+      <c r="AP51">
+        <v>3</v>
+      </c>
+      <c r="AQ51">
+        <v>6</v>
+      </c>
+      <c r="AR51">
+        <v>1</v>
+      </c>
+      <c r="AS51">
+        <v>2</v>
+      </c>
+      <c r="AT51" t="str">
+        <v>BioNTech Marburg GmbH → ValueMeds Distribution → Mount Sinai Health Pharmacy</v>
+      </c>
+      <c r="AU51">
+        <v>0</v>
+      </c>
+      <c r="AV51" t="str">
+        <v/>
+      </c>
+      <c r="AW51" t="str">
+        <v/>
+      </c>
+      <c r="AX51" t="str">
+        <v/>
+      </c>
+      <c r="AY51">
+        <v>0</v>
+      </c>
+      <c r="AZ51">
+        <v>0</v>
+      </c>
+      <c r="BA51">
+        <v>0</v>
+      </c>
+      <c r="BB51">
+        <v>0</v>
+      </c>
+      <c r="BC51">
+        <v>0</v>
+      </c>
+      <c r="BD51">
+        <v>0</v>
+      </c>
+      <c r="BE51">
+        <v>0</v>
+      </c>
+      <c r="BF51">
+        <v>0</v>
+      </c>
+      <c r="BG51" t="str">
+        <v/>
+      </c>
+      <c r="BH51" t="str">
+        <v/>
+      </c>
+      <c r="BI51" t="str">
+        <v/>
+      </c>
+      <c r="BJ51" t="str">
+        <v/>
+      </c>
+      <c r="BK51" t="str">
+        <v/>
+      </c>
+      <c r="BL51" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:BL51"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D10"/>
   <sheetData>
     <row r="1">
